--- a/reports/AEGIS_2026-06-25.xlsx
+++ b/reports/AEGIS_2026-06-25.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horizon Matrix" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Performance" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Why Picked" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor Snapshot" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statistics" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
@@ -22861,7 +22861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22872,7 +22872,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -22882,12 +22882,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Observed</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Used by Strategy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Contribution</t>
         </is>
       </c>
     </row>
@@ -22899,22 +22904,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Low trailing volatility</t>
+          <t>Above 20/50/100/200 EMA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lowest-vol set</t>
+          <t>Yes/Yes/Yes/Yes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -22926,22 +22936,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HRP cluster weight</t>
+          <t>50 vs 200 EMA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -22953,22 +22968,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sector cap &lt;= 2</t>
+          <t>RSI(14)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>diversified</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -22980,22 +23000,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Regime exposure</t>
+          <t>ROC(20)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -23007,22 +23032,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3M momentum</t>
+          <t>Momentum(10)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+8.6%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -23034,22 +23064,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Relative strength vs Nifty</t>
+          <t>Rel strength vs Nifty (3M)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>top 41%</t>
+          <t>+7.0%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -23061,22 +23096,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Above 200-DMA</t>
+          <t>Rel strength vs Sector (3M)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>+4.6%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -23088,22 +23128,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Trend strength</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ROE / PE / EPS / Debt</t>
+          <t>ADX(14)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>no point-in-time data</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -23115,22 +23160,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>News / earnings / events</t>
+          <t>Realised vol (20d, ann.)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Positive (low-vol = the driver)</t>
         </is>
       </c>
     </row>
@@ -23142,238 +23192,283 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RSI / MACD / ADX</t>
+          <t>ATR(14) %</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>not in model</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Low trailing volatility</t>
+          <t>Bollinger band width</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>lowest-vol set</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HRP cluster weight</t>
+          <t>Volume spike (vs 20d)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>0.8x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sector cap &lt;= 2</t>
+          <t>OBV trend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>diversified</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Regime exposure</t>
+          <t>HRP cluster weight</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3M momentum</t>
+          <t>Sector cap &lt;= 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+13.2%</t>
+          <t>diversified</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Macro</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Relative strength vs Nifty</t>
+          <t>Regime exposure</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>top 30%</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Fundamental</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Above 200-DMA</t>
+          <t>ROE/PE/EPS/Debt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not Evaluated</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>no PIT data</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>News/Events</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ROE / PE / EPS / Debt</t>
+          <t>earnings/orders/upgrades</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>no point-in-time data</t>
+          <t>Not Evaluated</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>no data</t>
         </is>
       </c>
     </row>
@@ -23385,22 +23480,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>News / earnings / events</t>
+          <t>Above 20/50/100/200 EMA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>Yes/Yes/Yes/Yes</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -23412,331 +23512,391 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RSI / MACD / ADX</t>
+          <t>50 vs 200 EMA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>not in model</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Low trailing volatility</t>
+          <t>RSI(14)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>lowest-vol set</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HRP cluster weight</t>
+          <t>ROC(20)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sector cap &lt;= 2</t>
+          <t>Momentum(10)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>diversified</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Regime exposure</t>
+          <t>Rel strength vs Nifty (3M)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>+11.6%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3M momentum</t>
+          <t>Rel strength vs Sector (3M)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Trend strength</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Relative strength vs Nifty</t>
+          <t>ADX(14)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>top 58%</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Above 200-DMA</t>
+          <t>Realised vol (20d, ann.)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Positive (low-vol = the driver)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ROE / PE / EPS / Debt</t>
+          <t>ATR(14) %</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>no point-in-time data</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>News / earnings / events</t>
+          <t>Bollinger band width</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RSI / MACD / ADX</t>
+          <t>Volume spike (vs 20d)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>not in model</t>
+          <t>0.6x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Low trailing volatility</t>
+          <t>OBV trend</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>lowest-vol set</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -23746,24 +23906,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -23778,19 +23943,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Macro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -23805,1249 +23975,3532 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Fundamental</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3M momentum</t>
+          <t>ROE/PE/EPS/Debt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>Not Evaluated</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>no PIT data</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>News/Events</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Relative strength vs Nifty</t>
+          <t>earnings/orders/upgrades</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>top 92%</t>
+          <t>Not Evaluated</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>no data</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Above 200-DMA</t>
+          <t>Above 20/50/100/200 EMA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Yes/Yes/Yes/Yes</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>info</t>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ROE / PE / EPS / Debt</t>
+          <t>50 vs 200 EMA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>no point-in-time data</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>News / earnings / events</t>
+          <t>RSI(14)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RSI / MACD / ADX</t>
+          <t>ROC(20)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>not in model</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Low trailing volatility</t>
+          <t>Momentum(10)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lowest-vol set</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HRP cluster weight</t>
+          <t>Rel strength vs Nifty (3M)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sector cap &lt;= 2</t>
+          <t>Rel strength vs Sector (3M)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>diversified</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Trend strength</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Regime exposure</t>
+          <t>ADX(14)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3M momentum</t>
+          <t>Realised vol (20d, ann.)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Positive (low-vol = the driver)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Relative strength vs Nifty</t>
+          <t>ATR(14) %</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>top 57%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Above 200-DMA</t>
+          <t>Bollinger band width</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>info</t>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ROE / PE / EPS / Debt</t>
+          <t>Volume spike (vs 20d)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>no point-in-time data</t>
+          <t>0.9x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>News / earnings / events</t>
+          <t>OBV trend</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RSI / MACD / ADX</t>
+          <t>HRP cluster weight</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>not in model</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Low trailing volatility</t>
+          <t>Sector cap &lt;= 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>lowest-vol set</t>
+          <t>diversified</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Macro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HRP cluster weight</t>
+          <t>Regime exposure</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Fundamental</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sector cap &lt;= 2</t>
+          <t>ROE/PE/EPS/Debt</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>diversified</t>
+          <t>Not Evaluated</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>no PIT data</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>News/Events</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Regime exposure</t>
+          <t>earnings/orders/upgrades</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Not Evaluated</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>no data</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3M momentum</t>
+          <t>Above 20/50/100/200 EMA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>Yes/No/No/No</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Relative strength vs Nifty</t>
+          <t>50 vs 200 EMA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>top 66%</t>
+          <t>Death</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Above 200-DMA</t>
+          <t>RSI(14)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>info</t>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ROE / PE / EPS / Debt</t>
+          <t>ROC(20)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>no point-in-time data</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>News / earnings / events</t>
+          <t>Momentum(10)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RSI / MACD / ADX</t>
+          <t>Rel strength vs Nifty (3M)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>not in model</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Low trailing volatility</t>
+          <t>Rel strength vs Sector (3M)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>lowest-vol set</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Trend strength</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HRP cluster weight</t>
+          <t>ADX(14)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sector cap &lt;= 2</t>
+          <t>Realised vol (20d, ann.)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>diversified</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Positive (low-vol = the driver)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Regime exposure</t>
+          <t>ATR(14) %</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>3M momentum</t>
+          <t>Bollinger band width</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Relative strength vs Nifty</t>
+          <t>Volume spike (vs 20d)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>top 73%</t>
+          <t>0.6x</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Above 200-DMA</t>
+          <t>OBV trend</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>rising</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>info</t>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ROE / PE / EPS / Debt</t>
+          <t>HRP cluster weight</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>no point-in-time data</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>News / earnings / events</t>
+          <t>Sector cap &lt;= 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>diversified</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Macro</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RSI / MACD / ADX</t>
+          <t>Regime exposure</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>not in model</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Fundamental</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Low trailing volatility</t>
+          <t>ROE/PE/EPS/Debt</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>lowest-vol set</t>
+          <t>Not Evaluated</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>no PIT data</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>News/Events</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HRP cluster weight</t>
+          <t>earnings/orders/upgrades</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>Not Evaluated</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>no data</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sector cap &lt;= 2</t>
+          <t>Above 20/50/100/200 EMA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>diversified</t>
+          <t>Yes/Yes/Yes/Yes</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Regime exposure</t>
+          <t>50 vs 200 EMA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Death</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3M momentum</t>
+          <t>RSI(14)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Relative strength vs Nifty</t>
+          <t>ROC(20)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>top 53%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CONTEXT (not a driver)</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Above 200-DMA</t>
+          <t>Momentum(10)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>+5.7%</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>info</t>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ROE / PE / EPS / Debt</t>
+          <t>Rel strength vs Nifty (3M)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>no point-in-time data</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NOT EVALUATED</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>News / earnings / events</t>
+          <t>Rel strength vs Sector (3M)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Trend strength</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ADX(14)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Realised vol (20d, ann.)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Positive (low-vol = the driver)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ATR(14) %</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Bollinger band width</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>8.9%</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Volume spike (vs 20d)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0.6x</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OBV trend</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>rising</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HRP cluster weight</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>14.9%</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sector cap &lt;= 2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>diversified</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Regime exposure</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Fundamental</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ROE/PE/EPS/Debt</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Not Evaluated</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>no PIT data</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>News/Events</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>earnings/orders/upgrades</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Not Evaluated</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Above 20/50/100/200 EMA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Yes/Yes/Yes/No</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>50 vs 200 EMA</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Death</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>RSI(14)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ROC(20)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Momentum(10)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Rel strength vs Nifty (3M)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>-1.5%</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Rel strength vs Sector (3M)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>-5.4%</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Trend strength</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ADX(14)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Realised vol (20d, ann.)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Positive (low-vol = the driver)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ATR(14) %</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Bollinger band width</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>12.3%</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Volume spike (vs 20d)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0.3x</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>OBV trend</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>rising</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>HRP cluster weight</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sector cap &lt;= 2</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>diversified</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Regime exposure</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Fundamental</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ROE/PE/EPS/Debt</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Not Evaluated</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>no PIT data</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>News/Events</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>earnings/orders/upgrades</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Not Evaluated</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Above 20/50/100/200 EMA</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>No/No/No/No</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>50 vs 200 EMA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Death</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>RSI(14)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ROC(20)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>-7.7%</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Momentum(10)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>-2.0%</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Rel strength vs Nifty (3M)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>-4.7%</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Rel strength vs Sector (3M)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>-13.3%</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Trend strength</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ADX(14)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Realised vol (20d, ann.)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Positive (low-vol = the driver)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ATR(14) %</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Bollinger band width</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>8.4%</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Volume spike (vs 20d)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2.9x</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>OBV trend</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>falling</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>HRP cluster weight</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Sector cap &lt;= 2</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>diversified</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Regime exposure</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Fundamental</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ROE/PE/EPS/Debt</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Not Evaluated</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>no PIT data</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>News/Events</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>earnings/orders/upgrades</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Not Evaluated</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>NOT EVALUATED</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>RSI / MACD / ADX</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>not in model</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Above 20/50/100/200 EMA</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Yes/Yes/Yes/Yes</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>50 vs 200 EMA</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Death</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>RSI(14)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ROC(20)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>+3.6%</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Momentum(10)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Rel strength vs Nifty (3M)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Rel strength vs Sector (3M)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Trend strength</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ADX(14)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Realised vol (20d, ann.)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Positive (low-vol = the driver)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ATR(14) %</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bollinger band width</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Volume spike (vs 20d)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>0.7x</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>OBV trend</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>rising</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>HRP cluster weight</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>11.2%</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Sector cap &lt;= 2</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>diversified</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Regime exposure</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Fundamental</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ROE/PE/EPS/Debt</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Not Evaluated</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>no PIT data</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>News/Events</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>earnings/orders/upgrades</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Not Evaluated</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>no data</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_2026-06-25.xlsx
+++ b/reports/AEGIS_2026-06-25.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,236 +468,258 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Recommendation ID</t>
+          <t>Workbook Version</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AEGIS-20260623-6M</t>
+          <t>AEGIS_2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Run Date</t>
+          <t>Recommendation Cycle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Market Data As Of</t>
+          <t>Run Date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Valid Until</t>
+          <t>Market Data As Of</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Valid Until</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AEGIS AEGIS Core v2.2</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Universe</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nifty-200</t>
+          <t>AEGIS AEGIS Core v2.2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Recommended Horizon</t>
+          <t>Universe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6M (confidence Medium)</t>
+          <t>Nifty-200</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Suggested Holding Window</t>
+          <t>Recommended Horizon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>6M (confidence Medium)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Portfolio Grade</t>
+          <t>Suggested Holding Window</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>6 months</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Recommendation Grade</t>
+          <t>Portfolio Grade</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Current Market</t>
+          <t>Recommendation Grade</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Exposure</t>
+          <t>Current Market</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Recommended Stocks</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>8</v>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Portfolio beat Nifty (history)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>13/19 (68%)</t>
-        </is>
+          <t>Recommended Stocks</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Historical median return (6M)</t>
+          <t>Portfolio beat Nifty (history)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>13/19 (68%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Historical win rate (6M)</t>
+          <t>Historical median return (6M)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>+7.5%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Expected drawdown</t>
+          <t>Historical win rate (6M)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>~11% (historical)</t>
+          <t>70%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Selection RQS (all history)</t>
+          <t>Expected drawdown</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.509 (~random)</t>
+          <t>~11% (historical)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Review Date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
+          <t>Cycles observed</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Selection RQS (all history)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.509 (~random)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Review Date</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>(expectations)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>historical, evidence-based — NOT forecasts/guarantees</t>
         </is>
@@ -1240,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T286"/>
+  <dimension ref="A1:U286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1336,10 +1358,15 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Why Picked</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1412,10 +1439,15 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1488,10 +1520,15 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1564,10 +1601,15 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1640,10 +1682,15 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1716,10 +1763,15 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1792,10 +1844,15 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1868,10 +1925,15 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -1944,10 +2006,15 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2020,10 +2087,15 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2096,10 +2168,15 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2172,10 +2249,15 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2248,10 +2330,15 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2324,10 +2411,15 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2400,10 +2492,15 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2476,10 +2573,15 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2552,10 +2654,15 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2628,10 +2735,15 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2704,10 +2816,15 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2780,10 +2897,15 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2856,10 +2978,15 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -2932,10 +3059,15 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3008,10 +3140,15 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3084,10 +3221,15 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3160,10 +3302,15 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3236,10 +3383,15 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3312,10 +3464,15 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3388,10 +3545,15 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3464,10 +3626,15 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3540,10 +3707,15 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3616,10 +3788,15 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3692,10 +3869,15 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3768,10 +3950,15 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3844,10 +4031,15 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3920,10 +4112,15 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -3996,10 +4193,15 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4072,10 +4274,15 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4148,10 +4355,15 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4224,10 +4436,15 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4300,10 +4517,15 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4376,10 +4598,15 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4452,10 +4679,15 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4528,10 +4760,15 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4604,10 +4841,15 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4680,10 +4922,15 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4756,10 +5003,15 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4832,10 +5084,15 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4908,10 +5165,15 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4984,10 +5246,15 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5060,10 +5327,15 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5136,10 +5408,15 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5212,10 +5489,15 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5288,10 +5570,15 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5364,10 +5651,15 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5440,10 +5732,15 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5516,10 +5813,15 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5592,10 +5894,15 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5668,10 +5975,15 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5742,10 +6054,15 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5818,10 +6135,15 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5892,10 +6214,15 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -5968,10 +6295,15 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6044,10 +6376,15 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6120,10 +6457,15 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6196,10 +6538,15 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6272,10 +6619,15 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6348,10 +6700,15 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6424,10 +6781,15 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6500,10 +6862,15 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6576,10 +6943,15 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6652,10 +7024,15 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6728,10 +7105,15 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6804,10 +7186,15 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6880,10 +7267,15 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -6956,10 +7348,15 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7032,10 +7429,15 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7108,10 +7510,15 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7184,10 +7591,15 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7260,10 +7672,15 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7336,10 +7753,15 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7412,10 +7834,15 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7488,10 +7915,15 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7564,10 +7996,15 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7640,10 +8077,15 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7716,10 +8158,15 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7792,10 +8239,15 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7868,10 +8320,15 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -7944,10 +8401,15 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8020,10 +8482,15 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8094,10 +8561,15 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8168,10 +8640,15 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8244,10 +8721,15 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8320,10 +8802,15 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8396,10 +8883,15 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="U94" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8472,10 +8964,15 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="U95" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8548,10 +9045,15 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="U96" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8624,10 +9126,15 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="U97" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8700,10 +9207,15 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="U98" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8776,10 +9288,15 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="U99" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8852,10 +9369,15 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -8928,10 +9450,15 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="U101" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9004,10 +9531,15 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="U102" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9080,10 +9612,15 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="U103" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9156,10 +9693,15 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="U104" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9232,10 +9774,15 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="U105" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9308,10 +9855,15 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="U106" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9384,10 +9936,15 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="U107" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9460,10 +10017,15 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="U108" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9536,10 +10098,15 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="U109" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9612,10 +10179,15 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="U110" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9688,10 +10260,15 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="U111" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9764,10 +10341,15 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="U112" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9840,10 +10422,15 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr">
+      <c r="U113" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9916,10 +10503,15 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="U114" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -9992,10 +10584,15 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="U115" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10068,10 +10665,15 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T116" t="inlineStr">
+      <c r="U116" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10144,10 +10746,15 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr">
+      <c r="U117" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10220,10 +10827,15 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="U118" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10296,10 +10908,15 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="U119" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10372,10 +10989,15 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="U120" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10448,10 +11070,15 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="U121" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10524,10 +11151,15 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
+      <c r="U122" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10600,10 +11232,15 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="U123" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10676,10 +11313,15 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr">
+      <c r="U124" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10752,10 +11394,15 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="U125" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10828,10 +11475,15 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="U126" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10904,10 +11556,15 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="U127" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -10980,10 +11637,15 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="U128" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11056,10 +11718,15 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T129" t="inlineStr">
+      <c r="U129" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11132,10 +11799,15 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr">
+      <c r="U130" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11208,10 +11880,15 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="U131" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11284,10 +11961,15 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T132" t="inlineStr">
+      <c r="U132" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11360,10 +12042,15 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T133" t="inlineStr">
+      <c r="U133" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11436,10 +12123,15 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T134" t="inlineStr">
+      <c r="U134" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11512,10 +12204,15 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T135" t="inlineStr">
+      <c r="U135" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11588,10 +12285,15 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="U136" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11664,10 +12366,15 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T137" t="inlineStr">
+      <c r="U137" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11740,10 +12447,15 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T138" t="inlineStr">
+      <c r="U138" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11816,10 +12528,15 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr">
+      <c r="U139" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11892,10 +12609,15 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T140" t="inlineStr">
+      <c r="U140" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -11968,10 +12690,15 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T141" t="inlineStr">
+      <c r="U141" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12044,10 +12771,15 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr">
+      <c r="U142" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12120,10 +12852,15 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T143" t="inlineStr">
+      <c r="U143" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12196,10 +12933,15 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T144" t="inlineStr">
+      <c r="U144" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12272,10 +13014,15 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T145" t="inlineStr">
+      <c r="U145" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12348,10 +13095,15 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T146" t="inlineStr">
+      <c r="U146" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12424,10 +13176,15 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr">
+      <c r="U147" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12500,10 +13257,15 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T148" t="inlineStr">
+      <c r="U148" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12576,10 +13338,15 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="U149" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12652,10 +13419,15 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T150" t="inlineStr">
+      <c r="U150" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12728,10 +13500,15 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T151" t="inlineStr">
+      <c r="U151" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12804,10 +13581,15 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr">
+      <c r="U152" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12880,10 +13662,15 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr">
+      <c r="U153" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -12956,10 +13743,15 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T154" t="inlineStr">
+      <c r="U154" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13032,10 +13824,15 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T155" t="inlineStr">
+      <c r="U155" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13108,10 +13905,15 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T156" t="inlineStr">
+      <c r="U156" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13184,10 +13986,15 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T157" t="inlineStr">
+      <c r="U157" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13260,10 +14067,15 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T158" t="inlineStr">
+      <c r="U158" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13336,10 +14148,15 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr">
+      <c r="U159" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13412,10 +14229,15 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T160" t="inlineStr">
+      <c r="U160" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13488,10 +14310,15 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T161" t="inlineStr">
+      <c r="U161" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13564,10 +14391,15 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr">
+      <c r="U162" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13640,10 +14472,15 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T163" t="inlineStr">
+      <c r="U163" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13716,10 +14553,15 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T164" t="inlineStr">
+      <c r="U164" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13790,10 +14632,15 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T165" t="inlineStr">
+      <c r="U165" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13866,10 +14713,15 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T166" t="inlineStr">
+      <c r="U166" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -13942,10 +14794,15 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T167" t="inlineStr">
+      <c r="U167" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14018,10 +14875,15 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T168" t="inlineStr">
+      <c r="U168" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14094,10 +14956,15 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T169" t="inlineStr">
+      <c r="U169" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14170,10 +15037,15 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T170" t="inlineStr">
+      <c r="U170" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14246,10 +15118,15 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T171" t="inlineStr">
+      <c r="U171" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14322,10 +15199,15 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T172" t="inlineStr">
+      <c r="U172" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14398,10 +15280,15 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T173" t="inlineStr">
+      <c r="U173" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14474,10 +15361,15 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T174" t="inlineStr">
+      <c r="U174" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14550,10 +15442,15 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T175" t="inlineStr">
+      <c r="U175" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14626,10 +15523,15 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T176" t="inlineStr">
+      <c r="U176" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14702,10 +15604,15 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T177" t="inlineStr">
+      <c r="U177" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14778,10 +15685,15 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T178" t="inlineStr">
+      <c r="U178" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14854,10 +15766,15 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr">
+      <c r="U179" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -14930,10 +15847,15 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr">
+      <c r="U180" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15006,10 +15928,15 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T181" t="inlineStr">
+      <c r="U181" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15082,10 +16009,15 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T182" t="inlineStr">
+      <c r="U182" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15158,10 +16090,15 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T183" t="inlineStr">
+      <c r="U183" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15234,10 +16171,15 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T184" t="inlineStr">
+      <c r="U184" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15310,10 +16252,15 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T185" t="inlineStr">
+      <c r="U185" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15386,10 +16333,15 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T186" t="inlineStr">
+      <c r="U186" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15462,10 +16414,15 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T187" t="inlineStr">
+      <c r="U187" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15538,10 +16495,15 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T188" t="inlineStr">
+      <c r="U188" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15614,10 +16576,15 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T189" t="inlineStr">
+      <c r="U189" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15690,10 +16657,15 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr">
+      <c r="U190" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15766,10 +16738,15 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T191" t="inlineStr">
+      <c r="U191" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15842,10 +16819,15 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T192" t="inlineStr">
+      <c r="U192" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15918,10 +16900,15 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T193" t="inlineStr">
+      <c r="U193" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -15994,10 +16981,15 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T194" t="inlineStr">
+      <c r="U194" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16070,10 +17062,15 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T195" t="inlineStr">
+      <c r="U195" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16146,10 +17143,15 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T196" t="inlineStr">
+      <c r="U196" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16222,10 +17224,15 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T197" t="inlineStr">
+      <c r="U197" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16298,10 +17305,15 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T198" t="inlineStr">
+      <c r="U198" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16374,10 +17386,15 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T199" t="inlineStr">
+      <c r="U199" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16450,10 +17467,15 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T200" t="inlineStr">
+      <c r="U200" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16526,10 +17548,15 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T201" t="inlineStr">
+      <c r="U201" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16602,10 +17629,15 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T202" t="inlineStr">
+      <c r="U202" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16678,10 +17710,15 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T203" t="inlineStr">
+      <c r="U203" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16754,10 +17791,15 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T204" t="inlineStr">
+      <c r="U204" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16830,10 +17872,15 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T205" t="inlineStr">
+      <c r="U205" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16906,10 +17953,15 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T206" t="inlineStr">
+      <c r="U206" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -16980,10 +18032,15 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T207" t="inlineStr">
+      <c r="U207" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17056,10 +18113,15 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T208" t="inlineStr">
+      <c r="U208" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17132,10 +18194,15 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T209" t="inlineStr">
+      <c r="U209" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17208,10 +18275,15 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T210" t="inlineStr">
+      <c r="U210" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17282,10 +18354,15 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T211" t="inlineStr">
+      <c r="U211" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17358,10 +18435,15 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T212" t="inlineStr">
+      <c r="U212" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17434,10 +18516,15 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T213" t="inlineStr">
+      <c r="U213" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17510,10 +18597,15 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T214" t="inlineStr">
+      <c r="U214" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17586,10 +18678,15 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T215" t="inlineStr">
+      <c r="U215" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17662,10 +18759,15 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T216" t="inlineStr">
+      <c r="U216" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17738,10 +18840,15 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T217" t="inlineStr">
+      <c r="U217" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17814,10 +18921,15 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T218" t="inlineStr">
+      <c r="U218" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17890,10 +19002,15 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T219" t="inlineStr">
+      <c r="U219" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -17966,10 +19083,15 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T220" t="inlineStr">
+      <c r="U220" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18042,10 +19164,15 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T221" t="inlineStr">
+      <c r="U221" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18116,10 +19243,15 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T222" t="inlineStr">
+      <c r="U222" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18192,10 +19324,15 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T223" t="inlineStr">
+      <c r="U223" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18266,10 +19403,15 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T224" t="inlineStr">
+      <c r="U224" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18340,10 +19482,15 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T225" t="inlineStr">
+      <c r="U225" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18416,10 +19563,15 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T226" t="inlineStr">
+      <c r="U226" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18492,10 +19644,15 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T227" t="inlineStr">
+      <c r="U227" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18568,10 +19725,15 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T228" t="inlineStr">
+      <c r="U228" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18644,10 +19806,15 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T229" t="inlineStr">
+      <c r="U229" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18720,10 +19887,15 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T230" t="inlineStr">
+      <c r="U230" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18796,10 +19968,15 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T231" t="inlineStr">
+      <c r="U231" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18872,10 +20049,15 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T232" t="inlineStr">
+      <c r="U232" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -18948,10 +20130,15 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T233" t="inlineStr">
+      <c r="U233" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19024,10 +20211,15 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T234" t="inlineStr">
+      <c r="U234" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19100,10 +20292,15 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T235" t="inlineStr">
+      <c r="U235" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19176,10 +20373,15 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T236" t="inlineStr">
+      <c r="U236" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19252,10 +20454,15 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T237" t="inlineStr">
+      <c r="U237" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19328,10 +20535,15 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T238" t="inlineStr">
+      <c r="U238" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19404,10 +20616,15 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T239" t="inlineStr">
+      <c r="U239" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19480,10 +20697,15 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T240" t="inlineStr">
+      <c r="U240" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19556,10 +20778,15 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T241" t="inlineStr">
+      <c r="U241" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19632,10 +20859,15 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T242" t="inlineStr">
+      <c r="U242" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19708,10 +20940,15 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T243" t="inlineStr">
+      <c r="U243" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19784,10 +21021,15 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T244" t="inlineStr">
+      <c r="U244" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19860,10 +21102,15 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T245" t="inlineStr">
+      <c r="U245" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -19936,10 +21183,15 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T246" t="inlineStr">
+      <c r="U246" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20012,10 +21264,15 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T247" t="inlineStr">
+      <c r="U247" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20088,10 +21345,15 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T248" t="inlineStr">
+      <c r="U248" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20164,10 +21426,15 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T249" t="inlineStr">
+      <c r="U249" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20240,10 +21507,15 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T250" t="inlineStr">
+      <c r="U250" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20316,10 +21588,15 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T251" t="inlineStr">
+      <c r="U251" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20392,10 +21669,15 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T252" t="inlineStr">
+      <c r="U252" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20466,10 +21748,15 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T253" t="inlineStr">
+      <c r="U253" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20540,10 +21827,15 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T254" t="inlineStr">
+      <c r="U254" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20614,10 +21906,15 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T255" t="inlineStr">
+      <c r="U255" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20688,10 +21985,15 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T256" t="inlineStr">
+      <c r="U256" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20764,10 +22066,15 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T257" t="inlineStr">
+      <c r="U257" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20840,10 +22147,15 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T258" t="inlineStr">
+      <c r="U258" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20916,10 +22228,15 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T259" t="inlineStr">
+      <c r="U259" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -20992,10 +22309,15 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T260" t="inlineStr">
+      <c r="U260" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21068,10 +22390,15 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T261" t="inlineStr">
+      <c r="U261" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21144,10 +22471,15 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T262" t="inlineStr">
+      <c r="U262" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21220,10 +22552,15 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T263" t="inlineStr">
+      <c r="U263" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21296,10 +22633,15 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T264" t="inlineStr">
+      <c r="U264" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21372,10 +22714,15 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T265" t="inlineStr">
+      <c r="U265" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21448,10 +22795,15 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T266" t="inlineStr">
+      <c r="U266" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21524,10 +22876,15 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T267" t="inlineStr">
+      <c r="U267" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21600,10 +22957,15 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T268" t="inlineStr">
+      <c r="U268" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21676,10 +23038,15 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T269" t="inlineStr">
+      <c r="U269" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21752,10 +23119,15 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T270" t="inlineStr">
+      <c r="U270" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21828,10 +23200,15 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T271" t="inlineStr">
+      <c r="U271" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21904,10 +23281,15 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T272" t="inlineStr">
+      <c r="U272" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -21980,10 +23362,15 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T273" t="inlineStr">
+      <c r="U273" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22056,10 +23443,15 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T274" t="inlineStr">
+      <c r="U274" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22132,10 +23524,15 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T275" t="inlineStr">
+      <c r="U275" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22208,10 +23605,15 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T276" t="inlineStr">
+      <c r="U276" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22284,10 +23686,15 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T277" t="inlineStr">
+      <c r="U277" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22360,10 +23767,15 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T278" t="inlineStr">
+      <c r="U278" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22436,10 +23848,15 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T279" t="inlineStr">
+      <c r="U279" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22512,10 +23929,15 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T280" t="inlineStr">
+      <c r="U280" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22588,10 +24010,15 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T281" t="inlineStr">
+      <c r="U281" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22664,10 +24091,15 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T282" t="inlineStr">
+      <c r="U282" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22740,10 +24172,15 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T283" t="inlineStr">
+      <c r="U283" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22816,10 +24253,15 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T284" t="inlineStr">
+      <c r="U284" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22892,10 +24334,15 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T285" t="inlineStr">
+      <c r="U285" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -22968,10 +24415,15 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
+          <t>low-vol + HRP + sector-cap + regime</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
           <t>quarterly rebalance</t>
         </is>
       </c>
-      <c r="T286" t="inlineStr">
+      <c r="U286" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -23423,7 +24875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23501,22 +24953,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sector leaders (3M)</t>
+          <t>Nifty 3M trend</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infra, Healthcare, Power</t>
+          <t>+1.6%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Global (S&amp;P 500 3M)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>+12.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sector leaders (3M)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Infra, Healthcare, Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Sector laggards (3M)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Metal, Cement, Energy</t>
         </is>
@@ -23539,82 +25015,82 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Allocation Order</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Rec ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Run Date</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Market Data As Of</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Entry Zone</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Allocated Rs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Weight %</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Market Data</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Valid Until</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>CMP</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Entry Zone</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Allocated Rs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Weight %</t>
+          <t>Review Date</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Suggested Holding Window</t>
+          <t>Expected Completion</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Review Date</t>
+          <t>Suggested Holding</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -23644,119 +25120,119 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Historical Cases</t>
+          <t>Risk Level</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Hist Cases</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Hist Win %</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Hist Median %</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Hist Avg %</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Hist Best %</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Hist Worst %</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hist Best %</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Level</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Expected DD %</t>
-        </is>
-      </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>Hist Avg Hold (d)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Risk Allocation Candidate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>AEGIS-20260623-6M</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Portfolio Constituent</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>allocation candidate — stock-alpha NOT validated (RQS~0.5)</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1901.6</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1873 - 1930</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>43737</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Telecom</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1901.6</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1873 - 1930</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>43737</v>
-      </c>
-      <c r="M2" t="n">
-        <v>23</v>
-      </c>
-      <c r="N2" t="n">
-        <v>14.9</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>6 months</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -23782,109 +25258,107 @@
           <t>No</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
         <v>13</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>69</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AB2" t="n">
         <v>-9.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC2" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>In 68% of past cycles this portfolio beat Nifty (avg +4.5%). BHARTIARTL appeared in 13 past portfolios, median +12.5%, win 69%. Risk-managed holding, not a return forecast.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Risk Allocation Candidate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>AEGIS-20260623-6M</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Portfolio Constituent</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>allocation candidate — stock-alpha NOT validated (RQS~0.5)</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2357.8</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2322 - 2393</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>40083</v>
+      </c>
+      <c r="I3" t="n">
+        <v>17</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2357.8</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2322 - 2393</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>40083</v>
-      </c>
-      <c r="M3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N3" t="n">
-        <v>13.9</v>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>6 months</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -23910,101 +25384,95 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>In 68% of past cycles this portfolio beat Nifty (avg +4.5%). LUPIN: no prior history. Risk-managed holding, not a return forecast.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Risk Allocation Candidate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>AEGIS-20260623-6M</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Portfolio Constituent</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>allocation candidate — stock-alpha NOT validated (RQS~0.5)</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>25570</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>25186 - 25954</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>25570</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ABBOTINDIA</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>25570</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>25186 - 25954</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>25570</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>13.6</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>6 months</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -24030,109 +25498,107 @@
           <t>No</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>24.6</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="AB4" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC4" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>In 68% of past cycles this portfolio beat Nifty (avg +4.5%). ABBOTINDIA appeared in 2 past portfolios, median +24.6%, win 100%. Risk-managed holding, not a return forecast.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Risk Allocation Candidate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>AEGIS-20260623-6M</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Portfolio Constituent</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>allocation candidate — stock-alpha NOT validated (RQS~0.5)</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>821</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>809 - 833</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>37768</v>
+      </c>
+      <c r="I5" t="n">
+        <v>46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>821</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>809 - 833</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>37768</v>
-      </c>
-      <c r="M5" t="n">
-        <v>46</v>
-      </c>
-      <c r="N5" t="n">
-        <v>12.7</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>6 months</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -24158,109 +25624,107 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
         <v>2</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>3.3</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.8</v>
       </c>
-      <c r="Z5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC5" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>In 68% of past cycles this portfolio beat Nifty (avg +4.5%). MARICO appeared in 2 past portfolios, median +3.3%, win 100%. Risk-managed holding, not a return forecast.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Risk Allocation Candidate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>AEGIS-20260623-6M</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Portfolio Constituent</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>allocation candidate — stock-alpha NOT validated (RQS~0.5)</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>8457</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8330 - 8584</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>33828</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>APOLLOHOSP</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>8457</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>8330 - 8584</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>33828</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>12.3</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>6 months</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -24286,109 +25750,107 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
         <v>4</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>75</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>5.9</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AB6" t="n">
         <v>-2.9</v>
       </c>
-      <c r="Z6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC6" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>In 68% of past cycles this portfolio beat Nifty (avg +4.5%). APOLLOHOSP appeared in 4 past portfolios, median +5.9%, win 75%. Risk-managed holding, not a return forecast.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Risk Allocation Candidate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>AEGIS-20260623-6M</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Portfolio Constituent</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>allocation candidate — stock-alpha NOT validated (RQS~0.5)</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1338.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1318 - 1358</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>33458</v>
+      </c>
+      <c r="I7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1338.3</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1318 - 1358</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>33458</v>
-      </c>
-      <c r="M7" t="n">
-        <v>25</v>
-      </c>
-      <c r="N7" t="n">
-        <v>11.2</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>6 months</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -24414,109 +25876,107 @@
           <t>No</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
         <v>8</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>75</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>5.3</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="AB7" t="n">
         <v>-7.4</v>
       </c>
-      <c r="Z7" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Running</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Risk Allocation Candidate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AEGIS-20260623-6M</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5241</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5162 - 5320</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>31446</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
         <v>11</v>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>In 68% of past cycles this portfolio beat Nifty (avg +4.5%). ICICIBANK appeared in 8 past portfolios, median +5.3%, win 75%. Risk-managed holding, not a return forecast.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AEGIS-20260623-6M</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Portfolio Constituent</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>allocation candidate — stock-alpha NOT validated (RQS~0.5)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>5241</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>5162 - 5320</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>31446</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>11</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>6 months</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -24542,109 +26002,107 @@
           <t>No</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
         <v>3</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>33</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>-7.7</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB8" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="Z8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC8" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>In 68% of past cycles this portfolio beat Nifty (avg +4.5%). BRITANNIA appeared in 3 past portfolios, median -7.7%, win 33%. Risk-managed holding, not a return forecast.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Risk Allocation Candidate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>AEGIS-20260623-6M</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Portfolio Constituent</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>allocation candidate — stock-alpha NOT validated (RQS~0.5)</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1833.7</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1806 - 1861</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>31173</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ICICIGI</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1833.7</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>1806 - 1861</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>31173</v>
-      </c>
-      <c r="M9" t="n">
-        <v>17</v>
-      </c>
-      <c r="N9" t="n">
-        <v>10.4</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>6 months</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -24670,37 +26128,35 @@
           <t>No</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
         <v>2</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>50</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>7.7</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AB9" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="Z9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC9" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Running</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>In 68% of past cycles this portfolio beat Nifty (avg +4.5%). ICICIGI appeared in 2 past portfolios, median +7.7%, win 50%. Risk-managed holding, not a return forecast.</t>
         </is>
       </c>
     </row>
@@ -30585,7 +32041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30639,6 +32095,16 @@
           <t>Beat Nifty</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Top Contributor</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Worst Contributor</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30681,6 +32147,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA (+4.3)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AIAENG (-0.5)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30723,6 +32199,16 @@
           <t>no</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>INFY (+0.9)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>COLPAL (-1.2)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30765,6 +32251,16 @@
           <t>no</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>COLPAL (+1.1)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NESTLEIND (-0.8)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30807,6 +32303,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>AIAENG (+3.0)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>INFY (-1.3)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30849,6 +32355,16 @@
           <t>no</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SUPREMEIND (+1.2)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>TCS (-0.3)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30891,6 +32407,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>IRFC (+6.5)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>RELAXO (-0.7)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30933,6 +32459,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ITC (+1.3)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>UBL (-1.1)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30975,6 +32511,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ICICIGI (+1.7)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (+0.1)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31017,6 +32563,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SUNDARMFIN (+2.6)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ASIANPAINT (-0.3)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31059,6 +32615,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LICI (+2.9)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MARUTI (-0.4)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31101,6 +32667,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MARUTI (+1.9)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>HINDUNILVR (-1.2)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31143,6 +32719,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>HINDUNILVR (+1.7)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MARUTI (+0.1)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31185,6 +32771,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PIIND (+1.7)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>TCS (-0.3)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31227,6 +32823,16 @@
           <t>no</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>EICHERMOT (+0.3)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>RELAXO (-2.6)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -31269,6 +32875,16 @@
           <t>no</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>MRF (+1.4)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>TCS (-1.3)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -31311,6 +32927,16 @@
           <t>no</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>MRF (+0.9)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>TCS (-0.6)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31353,6 +32979,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>MARUTI (+1.9)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>SHREECEM (-0.6)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31395,6 +33031,16 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SBIN (+1.2)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ITC (-1.7)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -31435,6 +33081,16 @@
       <c r="J20" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ONGC (+1.0)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>HDFCBANK (-1.9)</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_2026-06-25.xlsx
+++ b/reports/AEGIS_2026-06-25.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,77 +522,89 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rs300,000 (60%) · cash Rs200,000</t>
+          <t>Rs300,000 (60%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Allocation method</t>
+          <t>Remaining Cash (intentional)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equal-risk (HRP), sector-capped</t>
+          <t>Rs200,000 (40%) — regime-driven buffer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Historical win rate (6M)</t>
+          <t>Allocation method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>Equal-risk (HRP), sector-capped</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Historical median return (6M)</t>
+          <t>Historical win rate (6M)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>70%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Historical median return (6M)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>+7.5%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portfolio grade A (validated) · stock-alpha experimental (RQS 0.51)</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Portfolio grade A (validated) · stock-alpha experimental (RQS 0.51)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Reminder</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Historical = how similar past portfolios did. Evidence, NOT a forecast or guarantee.</t>
         </is>
@@ -609,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +687,20 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Max DD During Hold %</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Win Ratio</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Top Contributor</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Worst Contributor</t>
         </is>
@@ -733,12 +755,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>12/3</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>ABBOTINDIA (+4.3)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>AIAENG (-0.5)</t>
         </is>
@@ -793,12 +823,20 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>INFY (+0.9)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>COLPAL (-1.2)</t>
         </is>
@@ -853,12 +891,20 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>COLPAL (+1.1)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>NESTLEIND (-0.8)</t>
         </is>
@@ -913,12 +959,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6/9</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>AIAENG (+3.0)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>INFY (-1.3)</t>
         </is>
@@ -973,12 +1027,20 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>12/3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>SUPREMEIND (+1.2)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>TCS (-0.3)</t>
         </is>
@@ -1033,12 +1095,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>10/5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>IRFC (+6.5)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>RELAXO (-0.7)</t>
         </is>
@@ -1093,12 +1163,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>10/5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>ITC (+1.3)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>UBL (-1.1)</t>
         </is>
@@ -1153,12 +1231,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>15/0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>ICICIGI (+1.7)</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>KOTAKBANK (+0.1)</t>
         </is>
@@ -1213,12 +1299,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>11/4</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>SUNDARMFIN (+2.6)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>ASIANPAINT (-0.3)</t>
         </is>
@@ -1273,12 +1367,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>14/1</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>LICI (+2.9)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>MARUTI (-0.4)</t>
         </is>
@@ -1333,12 +1435,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>MARUTI (+1.9)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>HINDUNILVR (-1.2)</t>
         </is>
@@ -1393,12 +1503,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>15/0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>HINDUNILVR (+1.7)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>MARUTI (+0.1)</t>
         </is>
@@ -1453,12 +1571,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>11/4</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>PIIND (+1.7)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>TCS (-0.3)</t>
         </is>
@@ -1513,12 +1639,20 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>EICHERMOT (+0.3)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>RELAXO (-2.6)</t>
         </is>
@@ -1573,12 +1707,20 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>10/5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>MRF (+1.4)</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>TCS (-1.3)</t>
         </is>
@@ -1633,12 +1775,20 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>9/6</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>MRF (+0.9)</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>TCS (-0.6)</t>
         </is>
@@ -1693,12 +1843,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>10/5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>MARUTI (+1.9)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>SHREECEM (-0.6)</t>
         </is>
@@ -1753,12 +1911,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>6/9</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>SBIN (+1.2)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>ITC (-1.7)</t>
         </is>
@@ -1813,12 +1979,20 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>9/6</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>ONGC (+1.0)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>HDFCBANK (-1.9)</t>
         </is>
@@ -1835,7 +2009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1871,10 +2045,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Win Ratio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Max DD %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Largest Winner</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Largest Loser</t>
         </is>
@@ -1905,10 +2089,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>12/3</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>ABBOTINDIA (+4.3)</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>AIAENG (-0.5)</t>
         </is>
@@ -1939,10 +2131,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>INFY (+0.9)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>COLPAL (-1.2)</t>
         </is>
@@ -1973,10 +2173,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>4/11</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>COLPAL (+1.1)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>NESTLEIND (-0.8)</t>
         </is>
@@ -2007,10 +2215,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>6/9</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>AIAENG (+3.0)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>INFY (-1.3)</t>
         </is>
@@ -2041,10 +2257,18 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>12/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>SUPREMEIND (+1.2)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>TCS (-0.3)</t>
         </is>
@@ -2075,10 +2299,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>10/5</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>IRFC (+6.5)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>RELAXO (-0.7)</t>
         </is>
@@ -2109,10 +2341,18 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>10/5</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>ITC (+1.3)</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>UBL (-1.1)</t>
         </is>
@@ -2143,10 +2383,18 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>15/0</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>ICICIGI (+1.7)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>KOTAKBANK (+0.1)</t>
         </is>
@@ -2177,10 +2425,18 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>11/4</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>SUNDARMFIN (+2.6)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>ASIANPAINT (-0.3)</t>
         </is>
@@ -2211,10 +2467,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>14/1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>LICI (+2.9)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>MARUTI (-0.4)</t>
         </is>
@@ -2245,10 +2509,18 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>MARUTI (+1.9)</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>HINDUNILVR (-1.2)</t>
         </is>
@@ -2279,10 +2551,18 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>15/0</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>HINDUNILVR (+1.7)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>MARUTI (+0.1)</t>
         </is>
@@ -2313,10 +2593,18 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>11/4</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>PIIND (+1.7)</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>TCS (-0.3)</t>
         </is>
@@ -2347,10 +2635,18 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>4/11</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>EICHERMOT (+0.3)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>RELAXO (-2.6)</t>
         </is>
@@ -2381,10 +2677,18 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>10/5</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>MRF (+1.4)</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>TCS (-1.3)</t>
         </is>
@@ -2415,10 +2719,18 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>9/6</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>MRF (+0.9)</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>TCS (-0.6)</t>
         </is>
@@ -2449,10 +2761,18 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>10/5</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>MARUTI (+1.9)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>SHREECEM (-0.6)</t>
         </is>
@@ -2483,10 +2803,18 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>6/9</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>SBIN (+1.2)</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>ITC (-1.7)</t>
         </is>
@@ -2517,10 +2845,18 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>9/6</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>ONGC (+1.0)</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>HDFCBANK (-1.9)</t>
         </is>
@@ -2551,6 +2887,8 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26176,7 +26514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26454,10 +26792,34 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Recommendation Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Running — 8 Active · 0 Reviewed · 0 Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sample Confidence key</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>High &gt;=10 obs · Medium 5-9 · Low 2-4 · New 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>(expectations)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>historical, evidence-based — NOT forecasts/guarantees</t>
         </is>
@@ -26608,7 +26970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26654,120 +27016,125 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Entry Method</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Allocated Rs</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Generated</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Market Data</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Valid Until</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Valid for Entry Until</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Expected Completion</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Suggested Holding</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Confidence</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Construction Confidence</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>3M Momentum %</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Rel Strength vs Nifty</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Above 200-DMA</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Past Recs (count)</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>Past Observations</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Sample Confidence</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Win % (similar past recs)</t>
-        </is>
-      </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Median Ret % (similar past recs)</t>
+          <t>Historical Win % (Similar Recs)</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Avg Ret % (similar past recs)</t>
+          <t>Historical Median Return % (Similar Recs)</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Best % (similar past recs)</t>
+          <t>Historical Avg Return % (Similar Recs)</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Worst % (similar past recs)</t>
+          <t>Historical Best % (Similar Recs)</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Avg Hold d (similar past recs)</t>
+          <t>Historical Worst % (Similar Recs)</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Historical Avg Hold d (Similar Recs)</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -26794,7 +27161,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lowest-volatility name in Telecom under the sector cap; HRP-weighted</t>
+          <t>Lowest-vol name in Telecom (vol 21%); HRP-weighted (low correlation to book)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -26807,103 +27174,108 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1873 - 1930</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
+          <t>1851 - 1952</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Volatility band (~2 std-dev daily)</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>43737</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>23</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>14.9</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>2.5</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>top 57%</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>13</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>69</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>8.1</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>29.3</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>-9.5</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>63</v>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
@@ -26930,7 +27302,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lowest-volatility name in Pharma under the sector cap; HRP-weighted</t>
+          <t>Lowest-vol name in Pharma (vol 20%); above 200-DMA; HRP-weighted (low correlation to book)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -26943,115 +27315,120 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2322 - 2393</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+          <t>2298 - 2418</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Volatility band (~2 std-dev daily)</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>40083</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>17</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>13.9</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>2.4</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>top 58%</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>New — no history</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>New — no history</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>New — no history</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>New — no history</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>New — no history</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>New — no history</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
@@ -27078,7 +27455,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lowest-volatility name in Pharma under the sector cap; HRP-weighted</t>
+          <t>Lowest-vol name in Pharma (vol 22%); HRP-weighted (low correlation to book)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -27091,103 +27468,108 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25186 - 25954</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+          <t>24850 - 26290</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Volatility band (~2 std-dev daily)</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>25570</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>13.6</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>-3.1</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>top 73%</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>2</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>100</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>24.6</v>
       </c>
       <c r="AB4" t="n">
         <v>24.6</v>
       </c>
       <c r="AC4" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AD4" t="n">
         <v>31.6</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>63</v>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
@@ -27214,7 +27596,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lowest-volatility name in FMCG under the sector cap; HRP-weighted</t>
+          <t>Lowest-vol name in FMCG (vol 19%); above 200-DMA; diversifies the portfolio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -27227,103 +27609,108 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>809 - 833</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+          <t>801 - 841</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Volatility band (~2 std-dev daily)</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>37768</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>46</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>12.7</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>8.6</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>top 41%</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>2</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>100</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.3</v>
       </c>
       <c r="AB5" t="n">
         <v>3.3</v>
       </c>
       <c r="AC5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD5" t="n">
         <v>3.9</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>2.8</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>63</v>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
@@ -27350,7 +27737,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lowest-volatility name in Healthcare under the sector cap; HRP-weighted</t>
+          <t>Lowest-vol name in Healthcare (vol 20%); relative strength top 30% vs Nifty; above 200-DMA; diversifies the portfolio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -27363,103 +27750,108 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8330 - 8584</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+          <t>8242 - 8672</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Volatility band (~2 std-dev daily)</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>33828</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>12.3</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>13.2</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>top 30%</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>4</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>75</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>5.9</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>4.6</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>-2.9</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>63</v>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
@@ -27486,7 +27878,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lowest-volatility name in Financials under the sector cap; HRP-weighted</t>
+          <t>Lowest-vol name in Financials (vol 23%); diversifies the portfolio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -27499,103 +27891,108 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1318 - 1358</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+          <t>1300 - 1377</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Volatility band (~2 std-dev daily)</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>33458</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>25</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>11.2</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>3.8</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>top 53%</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>8</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>75</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>5.3</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>5.4</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>18.3</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>-7.4</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>63</v>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
@@ -27622,7 +28019,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lowest-volatility name in FMCG under the sector cap; HRP-weighted</t>
+          <t>Lowest-vol name in FMCG (vol 21%); diversifies the portfolio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -27635,103 +28032,108 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5162 - 5320</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+          <t>5103 - 5379</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Volatility band (~2 std-dev daily)</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>31446</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>6</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>-10.9</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>top 92%</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>3</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>33</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>-7.7</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>-2.7</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>9</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>63</v>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Running</t>
         </is>
@@ -27758,7 +28160,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lowest-volatility name in Financials under the sector cap; HRP-weighted</t>
+          <t>Lowest-vol name in Financials (vol 22%); diversifies the portfolio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -27771,103 +28173,108 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1806 - 1861</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+          <t>1782 - 1885</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Volatility band (~2 std-dev daily)</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>31173</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>17</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>10.4</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>6 months</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>0.1</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>top 66%</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>2</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>50</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>7.7</v>
       </c>
       <c r="AB9" t="n">
         <v>7.7</v>
       </c>
       <c r="AC9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AD9" t="n">
         <v>24.3</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>63</v>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>Running</t>
         </is>

--- a/reports/AEGIS_2026-06-25.xlsx
+++ b/reports/AEGIS_2026-06-25.xlsx
@@ -19,9 +19,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendation Replay" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategy Replay" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendation History" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statistics" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Badges" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About AEGIS" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Attribution" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Track Record" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yearly Quality" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statistics" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Badges" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About AEGIS" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26079,173 +26082,1383 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Times Held</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total Contribution %</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Contribution %</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Return %</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total cycles</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cycles beating Nifty</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>13 (68%)</t>
-        </is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cycles positive</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>14 (74%)</t>
-        </is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Avg portfolio return</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>+4.5%</t>
-        </is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Median portfolio return</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>+3.0%</t>
-        </is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Std deviation</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6.4%</t>
-        </is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E7" t="n">
+        <v>101.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Avg outperformance vs Nifty</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>+2.1%</t>
-        </is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Best cycle</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>+14.8%</t>
-        </is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Worst cycle</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>-6.4%</t>
-        </is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E10" t="n">
+        <v>24.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Avg winning cycle</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>+7.1%</t>
-        </is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E11" t="n">
+        <v>34.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Avg losing cycle</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-2.8%</t>
-        </is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Longest win streak</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>9 cycles</t>
-        </is>
+          <t>SUNDARMFIN</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E13" t="n">
+        <v>24.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Longest loss streak</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3 cycles</t>
-        </is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AIAENG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E25" t="n">
+        <v>18.91</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E26" t="n">
+        <v>11.66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8.94</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E30" t="n">
+        <v>25.86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.51</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>VINATIORGA</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>COROMANDEL</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E34" t="n">
+        <v>18.84</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E38" t="n">
+        <v>12.33</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9.029999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>15</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-5.41</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ATUL</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-11.19</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>9</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>9</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-4.28</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-7.03</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-6.94</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-5.63</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-9.43</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>15</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-10.88</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>RELAXO</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-10.85</v>
       </c>
     </row>
   </sheetData>
@@ -26259,126 +27472,2321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Times Recommended</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Detail</t>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Return %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Best %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Worst %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Win %</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Portfolio Strategy</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>VALIDATED</t>
-        </is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>15</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>grade A · beat Nifty 68% of cycles</t>
-        </is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stock Selection (alpha)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EXPERIMENTAL</t>
-        </is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RQS 0.51 ~ random · holdings, not bets</t>
-        </is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>53.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Recommendation Horizon</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HISTORICALLY TESTED</t>
-        </is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>all horizons backtested · best = 6M</t>
-        </is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>69.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Technical Context</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>COMPUTED (not a driver)</t>
-        </is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>momentum / rel-strength / 200-DMA shown for info</t>
-        </is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>66.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fundamental Analysis</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NOT EVALUATED</t>
-        </is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>no point-in-time data</t>
-        </is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>News / Events</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NOT EVALUATED</t>
-        </is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>no event database</t>
-        </is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2023-01-06</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2023-01-06</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2023-01-06</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AIAENG</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RELAXO</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H27" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ATUL</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2023-01-06</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>9</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VINATIORGA</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F43" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H44" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="H45" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2023-01-06</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F47" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H48" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F49" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H52" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2023-01-06</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="H54" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2023-01-06</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G59" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H59" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>31</v>
+      </c>
+      <c r="F60" t="n">
+        <v>31</v>
+      </c>
+      <c r="G60" t="n">
+        <v>31</v>
+      </c>
+      <c r="H60" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>COROMANDEL</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F63" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G63" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H63" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F64" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G64" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H64" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="F65" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G65" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="H65" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G66" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H66" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F67" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2022-01-03</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="F69" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SUNDARMFIN</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F71" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G71" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="H71" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -26387,6 +29795,533 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Picks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Return %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B3" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>83</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C5" t="n">
+        <v>37</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E5" t="n">
+        <v>62</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>58</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total cycles</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cycles beating Nifty</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13 (68%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cycles positive</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14 (74%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Avg portfolio return</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Median portfolio return</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>+3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Std deviation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avg outperformance vs Nifty</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>+2.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Best cycle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>+14.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Worst cycle</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-6.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Avg winning cycle</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Avg losing cycle</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Median winning cycle</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>+5.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Median losing cycle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-1.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Avg holding period</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6 months (63 trading days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Avg drawdown during hold</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Longest win streak</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9 cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Longest loss streak</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3 cycles</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Portfolio Strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VALIDATED</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>grade A · beat Nifty 68% of cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stock Selection (alpha)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EXPERIMENTAL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RQS 0.51 ~ random · holdings, not bets</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Recommendation Horizon</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HISTORICALLY TESTED</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>all horizons backtested · best = 6M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Technical Context</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COMPUTED (not a driver)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>momentum / rel-strength / 200-DMA shown for info</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fundamental Analysis</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NOT EVALUATED</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>no point-in-time data</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>News / Events</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NOT EVALUATED</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>no event database</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/reports/AEGIS_2026-06-25.xlsx
+++ b/reports/AEGIS_2026-06-25.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,7 +627,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>— TOP RISKS —</t>
+          <t>— HISTORICAL PORTFOLIO (19 cycles, 2021-2026) —</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -635,358 +635,175 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cycles beating Nifty</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lags in strong bull markets (low beta 0.37)</t>
+          <t>13/19 (68%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Median cycle return</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stock selection is NOT validated alpha (RQS ~0.5) — these are risk constituents</t>
+          <t>+3.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Avg cycle return</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Absolute returns survivorship-inflated; trust the relative edge vs Nifty</t>
+          <t>+4.5%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
+          <t>Money diary (ref capital)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Portfolio grade A (validated) · stock-alpha experimental</t>
+          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Recommended deployment now</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>60% (Weak regime)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>Buy ~Rs</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>Allocation Rs</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>Weight %</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>Hist Median Ret %</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>Prob +ve %</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>Why</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Strategy version</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AEGIS AEGIS Core v2.2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Telecom</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1901.6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>43737</v>
-      </c>
-      <c r="F24" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="G24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>69</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Low-risk Telecom holding; diversifies the portfolio; regime cautious (partial deploy); 13 similar past recs averaged +8%</t>
-        </is>
-      </c>
+          <t>— TOP RISKS —</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2357.8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>40083</v>
-      </c>
-      <c r="F25" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding; in an uptrend (above 200-DMA); diversifies the portfolio; regime cautious (partial deploy)</t>
+          <t>Lags in strong bull markets (low beta 0.37)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>25570</v>
-      </c>
-      <c r="E26" t="n">
-        <v>25570</v>
-      </c>
-      <c r="F26" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="G26" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding; diversifies the portfolio; regime cautious (partial deploy); 2 similar past recs averaged +25%</t>
+          <t>Stock selection is NOT validated alpha (RQS ~0.5) — these are risk constituents</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>821</v>
-      </c>
-      <c r="E27" t="n">
-        <v>37768</v>
-      </c>
-      <c r="F27" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="G27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>100</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding; in an uptrend (above 200-DMA); diversifies the portfolio; regime cautious (partial deploy); 2 similar past recs averaged +3%</t>
+          <t>Absolute returns survivorship-inflated; trust the relative edge vs Nifty</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>VALIDATION</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>8457</v>
-      </c>
-      <c r="E28" t="n">
-        <v>33828</v>
-      </c>
-      <c r="F28" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="G28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H28" t="n">
-        <v>75</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Low-risk Healthcare holding; in an uptrend (above 200-DMA); outperforming Nifty; diversifies the portfolio; regime cautious (partial deploy); 4 similar past recs averaged +5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1338.3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>33458</v>
-      </c>
-      <c r="F29" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>75</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding; diversifies the portfolio; regime cautious (partial deploy); 8 similar past recs averaged +5%</t>
+          <t>Portfolio grade A (validated) · stock-alpha experimental</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>5241</v>
-      </c>
-      <c r="E30" t="n">
-        <v>31446</v>
-      </c>
-      <c r="F30" t="n">
-        <v>11</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="H30" t="n">
-        <v>33</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding; diversifies the portfolio; regime cautious (partial deploy); 3 similar past recs averaged -3%</t>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>Buy ~Rs</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>Allocation Rs</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Weight %</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>Hist Median Ret %</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>Prob +ve %</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>Why</t>
         </is>
       </c>
     </row>
@@ -998,32 +815,295 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1901.6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>43737</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>69</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2357.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>40083</v>
+      </c>
+      <c r="F32" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>25570</v>
+      </c>
+      <c r="E33" t="n">
+        <v>25570</v>
+      </c>
+      <c r="F33" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>821</v>
+      </c>
+      <c r="E34" t="n">
+        <v>37768</v>
+      </c>
+      <c r="F34" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>8457</v>
+      </c>
+      <c r="E35" t="n">
+        <v>33828</v>
+      </c>
+      <c r="F35" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>75</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1338.3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>33458</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>75</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5241</v>
+      </c>
+      <c r="E37" t="n">
+        <v>31446</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>33</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D38" t="n">
         <v>1833.7</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E38" t="n">
         <v>31173</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F38" t="n">
         <v>10.4</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G38" t="n">
         <v>7.7</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H38" t="n">
         <v>50</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding; diversifies the portfolio; regime cautious (partial deploy); 2 similar past recs averaged +8%</t>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
         </is>
       </c>
     </row>
@@ -1038,13 +1118,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1069,75 +1149,105 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Hist Scenario Target</t>
+          <t>Hist Target</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Hist Median Return %</t>
+          <t>Upside %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Hist Median Ret %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Annualized %</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Risk / Reward (hist)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability Positive %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Probability &gt;10% %</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Best Case (hist) %</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Worst Case (hist) %</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Best Case %</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Worst Case %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Rel Strength</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Sector Score</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Recommended Holding</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Exit</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Allocation Rs</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Similar Past Cases</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
@@ -1174,57 +1284,83 @@
         <v>12.5</v>
       </c>
       <c r="H2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>1.3</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>69</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>54</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>29.3</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>-9.5</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>6 months</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Below 200-DMA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>In-line</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>59/100</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>6 months (6M)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="U2" t="n">
         <v>43737</v>
       </c>
-      <c r="P2" t="n">
+      <c r="V2" t="n">
         <v>23</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="W2" t="n">
         <v>14.9</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="Y2" t="n">
         <v>13</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Low-risk Telecom holding; diversifies the portfolio; regime cautious (partial deploy); 13 similar past recs averaged +8%</t>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1282,34 +1418,64 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Above 200-DMA</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>In-line</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>65/100</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6 months (6M)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="U3" t="n">
         <v>40083</v>
       </c>
-      <c r="P3" t="n">
+      <c r="V3" t="n">
         <v>17</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="W3" t="n">
         <v>13.9</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding; in an uptrend (above 200-DMA); diversifies the portfolio; regime cautious (partial deploy)</t>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1343,60 +1509,86 @@
       <c r="G4" t="n">
         <v>24.6</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>100</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>100</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>31.6</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>17.5</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>6 months</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Below 200-DMA</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lagging</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>65/100</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>6 months (6M)</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="U4" t="n">
         <v>25570</v>
       </c>
-      <c r="P4" t="n">
+      <c r="V4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="W4" t="n">
         <v>13.6</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="Y4" t="n">
         <v>2</v>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding; diversifies the portfolio; regime cautious (partial deploy); 2 similar past recs averaged +25%</t>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1423,60 +1615,86 @@
       <c r="G5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>100</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>3.9</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>2.8</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>6 months</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Above 200-DMA</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>In-line</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>29/100</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>6 months (6M)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="U5" t="n">
         <v>37768</v>
       </c>
-      <c r="P5" t="n">
+      <c r="V5" t="n">
         <v>46</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="W5" t="n">
         <v>12.7</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="Y5" t="n">
         <v>2</v>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding; in an uptrend (above 200-DMA); diversifies the portfolio; regime cautious (partial deploy); 2 similar past recs averaged +3%</t>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1504,50 +1722,76 @@
         <v>5.9</v>
       </c>
       <c r="H6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J6" t="n">
         <v>2.1</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>75</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>9.4</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>-2.9</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>6 months</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Above 200-DMA</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Outperforming</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>94/100</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>6 months (6M)</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="U6" t="n">
         <v>33828</v>
       </c>
-      <c r="P6" t="n">
+      <c r="V6" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="W6" t="n">
         <v>12.3</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="Y6" t="n">
         <v>4</v>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Low-risk Healthcare holding; in an uptrend (above 200-DMA); outperforming Nifty; diversifies the portfolio; regime cautious (partial deploy); 4 similar past recs averaged +5%</t>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1582,57 +1826,83 @@
         <v>5.3</v>
       </c>
       <c r="H7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>75</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>25</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>18.3</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>-7.4</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>6 months</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Below 200-DMA</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>In-line</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>35/100</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>6 months (6M)</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="U7" t="n">
         <v>33458</v>
       </c>
-      <c r="P7" t="n">
+      <c r="V7" t="n">
         <v>25</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="W7" t="n">
         <v>11.2</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="Y7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding; diversifies the portfolio; regime cautious (partial deploy); 8 similar past recs averaged +5%</t>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1660,50 +1930,76 @@
         <v>-7.7</v>
       </c>
       <c r="H8" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="J8" t="n">
         <v>-0.8</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>33</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>9</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>6 months</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Below 200-DMA</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lagging</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>29/100</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>6 months (6M)</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="U8" t="n">
         <v>31446</v>
       </c>
-      <c r="P8" t="n">
+      <c r="V8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="W8" t="n">
         <v>11</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="Y8" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding; diversifies the portfolio; regime cautious (partial deploy); 3 similar past recs averaged -3%</t>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -1738,50 +2034,76 @@
         <v>7.7</v>
       </c>
       <c r="H9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.9</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>50</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>50</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>24.3</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>6 months</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Below 200-DMA</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lagging</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>35/100</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>6 months (6M)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="U9" t="n">
         <v>31173</v>
       </c>
-      <c r="P9" t="n">
+      <c r="V9" t="n">
         <v>17</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="W9" t="n">
         <v>10.4</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="Y9" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding; diversifies the portfolio; regime cautious (partial deploy); 2 similar past recs averaged +8%</t>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2251,6 +2573,130 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>Expected values are HISTORICAL distributions of similar portfolios — evidence, NOT a forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>% of Capital</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Holdings</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16.5%</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12.9%</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CASH (intentional)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8 stocks / 5 sectors</t>
         </is>
       </c>
     </row>
@@ -27895,520 +28341,624 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Overall (all history)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Years covered</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6 (2021-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Investment cycles</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total stock-picks</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Win rate (picks)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Median pick return</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average pick return</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cycles beating Nifty</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13/19 (68%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Money diary (ref capital)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Picks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Winners</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>Losers</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Win %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Avg Return %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>Median %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>Best %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>Worst %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Cycles</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>Beat Nifty</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>Profit Rs</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="12">
+      <c r="A12" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B12" t="n">
         <v>30</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C12" t="n">
         <v>19</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D12" t="n">
         <v>11</v>
       </c>
-      <c r="E2" t="n">
-        <v>63</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="E12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F12" t="n">
         <v>4.6</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G12" t="n">
         <v>6</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H12" t="n">
         <v>31.6</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I12" t="n">
         <v>-14.9</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L12" t="n">
         <v>43738</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="13">
+      <c r="A13" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B13" t="n">
         <v>60</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C13" t="n">
         <v>32</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D13" t="n">
         <v>28</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E13" t="n">
         <v>53</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F13" t="n">
         <v>4.3</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H13" t="n">
         <v>101.2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I13" t="n">
         <v>-19.8</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J13" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L13" t="n">
         <v>93560</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="14">
+      <c r="A14" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B14" t="n">
         <v>60</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C14" t="n">
         <v>50</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E14" t="n">
         <v>83</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F14" t="n">
         <v>9.1</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G14" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H14" t="n">
         <v>34.7</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I14" t="n">
         <v>-16.5</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J14" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L14" t="n">
         <v>176947</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="15">
+      <c r="A15" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B15" t="n">
         <v>60</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C15" t="n">
         <v>37</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D15" t="n">
         <v>23</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E15" t="n">
         <v>62</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F15" t="n">
         <v>3.1</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G15" t="n">
         <v>2.6</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H15" t="n">
         <v>25.9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I15" t="n">
         <v>-26</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L15" t="n">
         <v>56158</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="16">
+      <c r="A16" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B16" t="n">
         <v>60</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C16" t="n">
         <v>35</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D16" t="n">
         <v>25</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E16" t="n">
         <v>58</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F16" t="n">
         <v>1.9</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G16" t="n">
         <v>1.5</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H16" t="n">
         <v>28.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I16" t="n">
         <v>-23.6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J16" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L16" t="n">
         <v>15954</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="17">
+      <c r="A17" t="n">
         <v>2026</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B17" t="n">
         <v>15</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C17" t="n">
         <v>9</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D17" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E17" t="n">
         <v>60</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F17" t="n">
         <v>2.2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G17" t="n">
         <v>2.5</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H17" t="n">
         <v>25.2</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I17" t="n">
         <v>-16.7</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L17" t="n">
         <v>7126</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Total cycles</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cycles beating Nifty</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>13 (68%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cycles positive</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>14 (74%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Avg portfolio return</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>+4.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Median portfolio return</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>+3.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Std deviation</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Avg outperformance vs Nifty</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>+2.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Best cycle</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>+14.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Worst cycle</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>-6.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Avg winning cycle</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>+7.1%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Avg losing cycle</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>-2.8%</t>
-        </is>
+          <t>Total cycles</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Median winning cycle</t>
+          <t>Cycles beating Nifty</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>13 (68%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Median losing cycle</t>
+          <t>Cycles positive</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>14 (74%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Avg holding period</t>
+          <t>Avg portfolio return</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6 months (63 trading days)</t>
+          <t>+4.5%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Avg drawdown during hold</t>
+          <t>Median portfolio return</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>+3.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Longest win streak</t>
+          <t>Std deviation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9 cycles</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Avg outperformance vs Nifty</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>+2.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Best cycle</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>+14.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Worst cycle</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-6.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Avg winning cycle</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Avg losing cycle</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Median winning cycle</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>+5.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Median losing cycle</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>-1.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Avg holding period</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6 months (63 trading days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Avg drawdown during hold</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Longest win streak</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>9 cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Longest loss streak</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>3 cycles</t>
         </is>

--- a/reports/AEGIS_2026-06-25.xlsx
+++ b/reports/AEGIS_2026-06-25.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,242 +683,163 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Recommended deployment now</t>
+          <t>Backtest CAGR (survivorship-inflated)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>60% (Weak regime)</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Strategy version</t>
+          <t>Backtest Sharpe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AEGIS AEGIS Core v2.2</t>
+          <t>2.03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>— TOP RISKS —</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>Backtest max drawdown</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11.2%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Recommended deployment now</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lags in strong bull markets (low beta 0.37)</t>
+          <t>60% (Weak regime)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Strategy version</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stock selection is NOT validated alpha (RQS ~0.5) — these are risk constituents</t>
+          <t>AEGIS AEGIS Core v2.2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Absolute returns survivorship-inflated; trust the relative edge vs Nifty</t>
-        </is>
-      </c>
+          <t>— TOP RISKS —</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Portfolio grade A (validated) · stock-alpha experimental</t>
+          <t>Lags in strong bull markets (low beta 0.37)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Stock selection is NOT validated alpha (RQS ~0.5) — these are risk constituents</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Strength</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>Buy ~Rs</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>Allocation Rs</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Weight %</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>Hist Median Ret %</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t>Prob +ve %</t>
-        </is>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>Why</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Absolute returns survivorship-inflated; trust the relative edge vs Nifty</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>VALIDATION</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Telecom</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1901.6</v>
-      </c>
-      <c r="E31" t="n">
-        <v>43737</v>
-      </c>
-      <c r="F31" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="G31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H31" t="n">
-        <v>69</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ACCUMULATE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>2357.8</v>
-      </c>
-      <c r="E32" t="n">
-        <v>40083</v>
-      </c>
-      <c r="F32" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Portfolio grade A (validated) · stock-alpha experimental</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ABBOTINDIA</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>25570</v>
-      </c>
-      <c r="E33" t="n">
-        <v>25570</v>
-      </c>
-      <c r="F33" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="G33" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="H33" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>Buy ~Rs</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>Allocation Rs</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>Weight %</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>Hist Median Ret %</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>Prob +ve %</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>Why</t>
         </is>
       </c>
     </row>
@@ -930,118 +851,122 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>821</v>
+        <v>1901.6</v>
       </c>
       <c r="E34" t="n">
-        <v>37768</v>
+        <v>43737</v>
       </c>
       <c r="F34" t="n">
-        <v>12.7</v>
+        <v>14.9</v>
       </c>
       <c r="G34" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8457</v>
+        <v>2357.8</v>
       </c>
       <c r="E35" t="n">
-        <v>33828</v>
+        <v>40083</v>
       </c>
       <c r="F35" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="G35" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H35" t="n">
-        <v>75</v>
+        <v>13.9</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.3%) • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1338.3</v>
+        <v>25570</v>
       </c>
       <c r="E36" t="n">
-        <v>33458</v>
+        <v>25570</v>
       </c>
       <c r="F36" t="n">
-        <v>11.2</v>
+        <v>13.6</v>
       </c>
       <c r="G36" t="n">
-        <v>5.3</v>
+        <v>24.6</v>
       </c>
       <c r="H36" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-8.6%) • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1050,60 +975,171 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5241</v>
+        <v>821</v>
       </c>
       <c r="E37" t="n">
-        <v>31446</v>
+        <v>37768</v>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>12.7</v>
       </c>
       <c r="G37" t="n">
-        <v>-7.7</v>
+        <v>3.3</v>
       </c>
       <c r="H37" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.5%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8457</v>
+      </c>
+      <c r="E38" t="n">
+        <v>33828</v>
+      </c>
+      <c r="F38" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H38" t="n">
+        <v>75</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+11.2%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1338.3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>33458</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>75</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.6%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5241</v>
+      </c>
+      <c r="E40" t="n">
+        <v>31446</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="H40" t="n">
+        <v>33</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.6%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D41" t="n">
         <v>1833.7</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E41" t="n">
         <v>31173</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F41" t="n">
         <v>10.4</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G41" t="n">
         <v>7.7</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H41" t="n">
         <v>50</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.5%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,125 +1165,155 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Score /100</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Buy Range</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Hist Target</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upside %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Hist Median Ret %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Annualized %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Risk / Reward (hist)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Probability Positive %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Probability &gt;10% %</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Best Case %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Worst Case %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Dist 200-DMA %</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Vol Pctile</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>52W Range Pos %</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Rel Strength</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Sector Score</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Today's Setup</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Recommended Holding</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Expected Exit</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Allocation Rs</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Similar Past Cases</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
@@ -1256,332 +1322,392 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>72</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Telecom</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1901.6</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1851 - 1952</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>2139</v>
-      </c>
-      <c r="G2" t="n">
-        <v>12.5</v>
       </c>
       <c r="H2" t="n">
         <v>12.5</v>
       </c>
       <c r="I2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>26.5</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>1.3</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>69</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>54</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>29.3</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>-9.5</v>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Below 200-DMA</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>66</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>36</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-2.6%)</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>In-line</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>59/100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>below 200-DMA -2.6%; calm vol (2th pctile); 36% of 52w range; RSI 66; sector rank 59/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>6 months (6M)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="AA2" t="n">
         <v>43737</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AB2" t="n">
         <v>23</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AC2" t="n">
         <v>14.9</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="n">
         <v>13</v>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>LUPIN</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>2357.8</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2298 - 2418</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Above 200-DMA</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>69</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>83</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Above 200-DMA (+9.3%)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>In-line</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>65/100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>above 200-DMA +9.3%; calm vol (1th pctile); near 52w high; RSI 69; sector rank 65/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>6 months (6M)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="AA3" t="n">
         <v>40083</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AB3" t="n">
         <v>17</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AC3" t="n">
         <v>13.9</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="AE3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.3%) • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>76</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>ABBOTINDIA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>25570</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>24850 - 26290</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>31853</v>
-      </c>
-      <c r="G4" t="n">
-        <v>24.6</v>
       </c>
       <c r="H4" t="n">
         <v>24.6</v>
       </c>
       <c r="I4" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J4" t="n">
         <v>55.2</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
-      </c>
-      <c r="K4" t="n">
-        <v>100</v>
       </c>
       <c r="L4" t="n">
         <v>100</v>
       </c>
       <c r="M4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N4" t="n">
         <v>31.6</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>17.5</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Below 200-DMA</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-8.6%)</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>Lagging</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>65/100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>below 200-DMA -8.6%; calm vol (4th pctile); near 52w low; RSI 40; sector rank 65/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>6 months (6M)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="AA4" t="n">
         <v>25570</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AB4" t="n">
         <v>1</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AC4" t="n">
         <v>13.6</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="AE4" t="n">
         <v>2</v>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-8.6%) • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
         </is>
       </c>
     </row>
@@ -1591,103 +1717,123 @@
           <t>STRONG BUY</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>MARICO</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>821</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>801 - 841</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>848</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.3</v>
       </c>
       <c r="H5" t="n">
         <v>3.3</v>
       </c>
       <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
         <v>6.8</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>No historical analogues yet (&lt;3 obs)</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>100</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3.9</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.8</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Above 200-DMA</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>56</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>86</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Above 200-DMA (+8.5%)</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>In-line</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>29/100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>above 200-DMA +8.5%; calm vol (0th pctile); near 52w high; RSI 56; sector rank 29/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>6 months (6M)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U5" t="n">
+      <c r="AA5" t="n">
         <v>37768</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AB5" t="n">
         <v>46</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
         <v>12.7</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="AE5" t="n">
         <v>2</v>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.5%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
@@ -1697,101 +1843,121 @@
           <t>STRONG BUY</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>8457</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>8242 - 8672</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>8959</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.9</v>
       </c>
       <c r="H6" t="n">
         <v>5.9</v>
       </c>
       <c r="I6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J6" t="n">
         <v>12.2</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>2.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>75</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>9.4</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>-2.9</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Above 200-DMA</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>96</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Above 200-DMA (+11.2%)</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>Outperforming</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>94/100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>above 200-DMA +11.2%; calm vol (1th pctile); near 52w high; RSI 63; sector rank 94/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>6 months (6M)</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="AA6" t="n">
         <v>33828</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AB6" t="n">
         <v>4</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AC6" t="n">
         <v>12.3</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="AE6" t="n">
         <v>4</v>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+11.2%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1801,101 +1967,121 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="n">
+        <v>64</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>1338.3</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>1300 - 1377</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1409</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.3</v>
       </c>
       <c r="H7" t="n">
         <v>5.3</v>
       </c>
       <c r="I7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J7" t="n">
         <v>10.9</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.7</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>75</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>25</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>18.3</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-7.4</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Below 200-DMA</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>78</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>47</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-0.6%)</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>In-line</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>35/100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>below 200-DMA -0.6%; calm vol (6th pctile); 47% of 52w range; RSI 78 (overbought); sector rank 35/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>6 months (6M)</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="AA7" t="n">
         <v>33458</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AB7" t="n">
         <v>25</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AC7" t="n">
         <v>11.2</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="AE7" t="n">
         <v>8</v>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.6%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1905,101 +2091,121 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>BRITANNIA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>5241</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>5103 - 5379</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>4835</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-7.7</v>
       </c>
       <c r="H8" t="n">
         <v>-7.7</v>
       </c>
       <c r="I8" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="J8" t="n">
         <v>-14.9</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>-0.8</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>33</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>9</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Below 200-DMA</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>69</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-9.6%)</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>Lagging</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>29/100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>below 200-DMA -9.6%; calm vol (2th pctile); near 52w low; RSI 69; sector rank 29/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>6 months (6M)</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="AA8" t="n">
         <v>31446</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AB8" t="n">
         <v>6</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AC8" t="n">
         <v>11</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="AE8" t="n">
         <v>3</v>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.6%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2009,101 +2215,121 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>1833.7</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>1782 - 1885</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1975</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.7</v>
       </c>
       <c r="H9" t="n">
         <v>7.7</v>
       </c>
       <c r="I9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J9" t="n">
         <v>16.1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>0.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>50</v>
       </c>
       <c r="L9" t="n">
         <v>50</v>
       </c>
       <c r="M9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" t="n">
         <v>24.3</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Below 200-DMA</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>62</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>39</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-2.5%)</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>Lagging</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>35/100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>below 200-DMA -2.5%; calm vol (3th pctile); 39% of 52w range; RSI 62; sector rank 35/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>6 months (6M)</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U9" t="n">
+      <c r="AA9" t="n">
         <v>31173</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AB9" t="n">
         <v>17</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AC9" t="n">
         <v>10.4</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="AE9" t="n">
         <v>2</v>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.5%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
         </is>
       </c>
     </row>
@@ -28341,7 +28567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28509,6 +28735,16 @@
           <t>Profit Rs</t>
         </is>
       </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Year Ret %</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>End Rs (from ref)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -28549,6 +28785,12 @@
       <c r="L12" t="n">
         <v>43738</v>
       </c>
+      <c r="M12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>542732</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -28589,6 +28831,12 @@
       <c r="L13" t="n">
         <v>93560</v>
       </c>
+      <c r="M13" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>600703</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -28629,6 +28877,12 @@
       <c r="L14" t="n">
         <v>176947</v>
       </c>
+      <c r="M14" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>722531</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -28669,6 +28923,12 @@
       <c r="L15" t="n">
         <v>56158</v>
       </c>
+      <c r="M15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>551527</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -28709,6 +28969,12 @@
       <c r="L16" t="n">
         <v>15954</v>
       </c>
+      <c r="M16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>531876</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -28748,6 +29014,12 @@
       </c>
       <c r="L17" t="n">
         <v>7126</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>504000</v>
       </c>
     </row>
     <row r="19">
@@ -28975,7 +29247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29065,10 +29337,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Evidence Score (0-100)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The Strength label is driven by a transparent score: historical win rate (30) + historical median return (30) + trend/relative-strength (20) + regime &amp; low-vol (20). &gt;=70 STRONG BUY, &gt;=55 BUY, &gt;=42 ACCUMULATE, else WATCH. HARD RULE: a negative historical median is always WATCH (never a BUY), even if held for diversification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sector Score (x/100)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Percentile rank of the stock's sector by 3-month sector momentum. CONTEXT only — it failed the incremental-value test, so it informs but does not drive selection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Today's Setup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Descriptive current-state facts (distance from 200-DMA, volatility percentile, 52-week range position, RSI, sector rank, regime). Context for 'why today', NOT a forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Holding period</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chosen from the backtested Horizon Matrix each run (currently 6M). Evidence-selected, not hand-set; it moves if the evidence moves. Per-STOCK horizons are NOT offered — small-sample horizon skill is ~random (RQS 0.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Number of holdings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Driven by how many names clear the low-vol + sector-cap filter (varies by breadth), NOT return-optimised. Tested: choosing N by trailing performance LOSES out-of-sample (Sharpe 0.95 vs 1.24) — so N is risk-driven, and the validated de-risking lever is exposure/cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>What it does NOT do</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Predict returns or pick 'winners'. Returns are ~unpredictable on this data; risk is. AEGIS forecasts risk, not direction.</t>
         </is>

--- a/reports/AEGIS_2026-06-25.xlsx
+++ b/reports/AEGIS_2026-06-25.xlsx
@@ -13,9 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Performance" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtested Trades" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holding Period Options" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hold a 8-stock risk-managed portfolio</t>
+          <t>Hold a 12-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -492,7 +493,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6M (6 months)</t>
+          <t>2M (2 months)</t>
         </is>
       </c>
     </row>
@@ -540,7 +541,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -560,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>67%</t>
         </is>
       </c>
     </row>
@@ -572,7 +573,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>+2.5%</t>
         </is>
       </c>
     </row>
@@ -584,7 +585,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rs537,500</t>
+          <t>Rs512,500</t>
         </is>
       </c>
     </row>
@@ -596,7 +597,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rs616,000</t>
+          <t>Rs602,000</t>
         </is>
       </c>
     </row>
@@ -608,7 +609,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rs433,500</t>
+          <t>Rs458,000</t>
         </is>
       </c>
     </row>
@@ -731,193 +732,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Strategy version</t>
+          <t>Portfolio process confidence</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AEGIS AEGIS Core v2.2</t>
+          <t>94% (validated process)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>— TOP RISKS —</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>Confidence note</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Portfolio confidence = the validated PROCESS. Per-stock 'Rec Confidence %' in Today's sheet = strength of that one pick's evidence — a different, weaker thing.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Strategy version</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lags in strong bull markets (low beta 0.37)</t>
+          <t>AEGIS AEGIS Core v2.2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Stock selection is NOT validated alpha (RQS ~0.5) — these are risk constituents</t>
-        </is>
-      </c>
+          <t>— TOP RISKS —</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Absolute returns survivorship-inflated; trust the relative edge vs Nifty</t>
+          <t>Lags in strong bull markets (low beta 0.37)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Stock selection is NOT validated alpha (RQS ~0.5) — these are risk constituents</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Absolute returns survivorship-inflated; trust the relative edge vs Nifty</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>VALIDATION</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Portfolio grade A (validated) · stock-alpha experimental</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>Buy ~Rs</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
         <is>
           <t>Allocation Rs</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F35" s="1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>Hist Median Ret %</t>
         </is>
       </c>
-      <c r="H33" s="1" t="inlineStr">
+      <c r="H35" s="1" t="inlineStr">
         <is>
           <t>Prob +ve %</t>
         </is>
       </c>
-      <c r="I33" s="1" t="inlineStr">
+      <c r="I35" s="1" t="inlineStr">
         <is>
           <t>Why</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Telecom</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1901.6</v>
-      </c>
-      <c r="E34" t="n">
-        <v>43737</v>
-      </c>
-      <c r="F34" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="G34" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>69</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>2357.8</v>
-      </c>
-      <c r="E35" t="n">
-        <v>40083</v>
-      </c>
-      <c r="F35" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.3%) • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -944,7 +891,7 @@
         <v>25570</v>
       </c>
       <c r="F36" t="n">
-        <v>13.6</v>
+        <v>11.3</v>
       </c>
       <c r="G36" t="n">
         <v>24.6</v>
@@ -961,37 +908,41 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>821</v>
+        <v>2357.8</v>
       </c>
       <c r="E37" t="n">
-        <v>37768</v>
+        <v>33009</v>
       </c>
       <c r="F37" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H37" t="n">
-        <v>100</v>
+        <v>11</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.5%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.3%) • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1015,10 +966,10 @@
         <v>8457</v>
       </c>
       <c r="E38" t="n">
-        <v>33828</v>
+        <v>25371</v>
       </c>
       <c r="F38" t="n">
-        <v>12.3</v>
+        <v>10.9</v>
       </c>
       <c r="G38" t="n">
         <v>5.9</v>
@@ -1035,37 +986,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1338.3</v>
+        <v>1901.6</v>
       </c>
       <c r="E39" t="n">
-        <v>33458</v>
+        <v>30426</v>
       </c>
       <c r="F39" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="G39" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="H39" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.6%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
@@ -1089,10 +1040,10 @@
         <v>5241</v>
       </c>
       <c r="E40" t="n">
-        <v>31446</v>
+        <v>26205</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
         <v>-7.7</v>
@@ -1109,37 +1060,465 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>821</v>
+      </c>
+      <c r="E41" t="n">
+        <v>27095</v>
+      </c>
+      <c r="F41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.5%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ACCUMULATE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1309.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>22262</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>62</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D43" t="n">
         <v>1833.7</v>
       </c>
-      <c r="E41" t="n">
-        <v>31173</v>
-      </c>
-      <c r="F41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="E43" t="n">
+        <v>20171</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G43" t="n">
         <v>7.7</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H43" t="n">
         <v>50</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Low-risk Financials holding (low vol) • below 200-dma (-2.5%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1338.3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>17398</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>75</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.6%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>17136</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • above 200-dma (+2.7%) • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>291.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16349</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>50</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • above 200-dma (+2.1%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>25035</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="H47" t="n">
+        <v>40</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Low-risk Cement holding (low vol) • below 200-dma (-5.5%) • sector strength 12/100 • regime cautious (partial deploy) • 5 similar past recs: 40% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What AEGIS is</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A risk-managed PORTFOLIO engine: low-volatility selection + HRP weighting + sector cap + market-regime exposure timing. Rebalances quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>What is validated</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The PORTFOLIO process (grade A): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>What is NOT validated</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Individual stock-picking ALPHA. Selection RQS 0.51 ~ random — picks are portfolio CONSTITUENTS, not proven winners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>What AEGIS is NOT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Not a tip sheet, not a multibagger finder, not a return predictor. It does not forecast which stock will rise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Exit philosophy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Process-based: hold to the quarterly review/rebalance. No fixed stop-loss (unvalidated). Emergency exit only on fraud/delisting/regime-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Review frequency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly. Recommendation valid ~1 week from generation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Not evaluated (no data)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fundamentals (ROE/PE/EPS), news/events, earnings, institutional flow. Shown as 'Not Evaluated' — never invented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Honest caveat</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Absolute return levels are survivorship-inflated; trust the RELATIVE edge vs Nifty. Forward paper (live cycles) is the real, ongoing test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EVIDENCE STATUS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Portfolio Strategy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VALIDATED — grade A · beat Nifty 68% of cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stock Selection (alpha)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EXPERIMENTAL — RQS 0.51 ~ random · holdings, not bets</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Recommendation Horizon</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HISTORICALLY TESTED — all horizons backtested · best = 2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Technical Context</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COMPUTED (not a driver) — momentum / rel-strength / 200-DMA shown for info</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fundamental Analysis</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NOT EVALUATED — no point-in-time data</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>News / Events</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NOT EVALUATED — no event database</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1275,45 +1654,65 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>Why This vs Alternatives</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Rec Confidence %</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Recommended Holding</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Expected Exit</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Valid Until</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Allocation Rs</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Similar Past Cases</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
@@ -1326,120 +1725,140 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1901.6</v>
+        <v>25570</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1851 - 1952</t>
+          <t>24850 - 26290</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2139</v>
+        <v>31853</v>
       </c>
       <c r="H2" t="n">
-        <v>12.5</v>
+        <v>24.6</v>
       </c>
       <c r="I2" t="n">
-        <v>12.5</v>
+        <v>24.6</v>
       </c>
       <c r="J2" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.3</v>
+        <v>273.7</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
       </c>
       <c r="L2" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="N2" t="n">
-        <v>29.3</v>
+        <v>31.6</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.5</v>
+        <v>17.5</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.6</v>
+        <v>-8.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="R2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-8.6%)</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Lagging</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>65/100</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>below 200-DMA -8.6%; calm vol (4th pctile); near 52w low; RSI 40; sector rank 65/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 76; CIPLA: 91, TORNTPHARM: 83, SUNPHARMA: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>25570</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
         <v>2</v>
       </c>
-      <c r="S2" t="n">
-        <v>36</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-2.6%)</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>In-line</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>59/100</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>below 200-DMA -2.6%; calm vol (2th pctile); 36% of 52w range; RSI 66; sector rank 59/100; regime cautious</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>6 months (6M)</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>43737</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-8.6%) • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
         </is>
       </c>
     </row>
@@ -1549,37 +1968,55 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>6 months (6M)</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 55; CIPLA: 91, TORNTPHARM: 83, ABBOTINDIA: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>65</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>40083</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13.9</v>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>33009</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
           <t>New</t>
         </is>
       </c>
-      <c r="AE3" t="n">
+      <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.3%) • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
@@ -1592,122 +2029,138 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25570</v>
+        <v>8457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24850 - 26290</t>
+          <t>8242 - 8672</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>31853</v>
+        <v>8959</v>
       </c>
       <c r="H4" t="n">
-        <v>24.6</v>
+        <v>5.9</v>
       </c>
       <c r="I4" t="n">
-        <v>24.6</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
+        <v>41.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.1</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>31.6</v>
+        <v>9.4</v>
       </c>
       <c r="O4" t="n">
-        <v>17.5</v>
+        <v>-2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>-8.6</v>
+        <v>11.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>96</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Above 200-DMA (+11.2%)</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Outperforming</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>94/100</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>above 200-DMA +11.2%; calm vol (1th pctile); near 52w high; RSI 63; sector rank 94/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 80; FORTIS: 60, MAXHEALTH: 60, LALPATHLAB: 55</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>25371</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
         <v>4</v>
       </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-8.6%)</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Lagging</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>65/100</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>below 200-DMA -8.6%; calm vol (4th pctile); near 52w low; RSI 40; sector rank 65/100; regime cautious</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>6 months (6M)</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA4" t="n">
-        <v>25570</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-8.6%) • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+11.2%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1718,70 +2171,68 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>821</v>
+        <v>1901.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>801 - 841</t>
+          <t>1851 - 1952</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>848</v>
+        <v>2139</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="J5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
+        <v>102.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.3</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>29.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>-9.5</v>
       </c>
       <c r="P5" t="n">
-        <v>8.5</v>
+        <v>-2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.5%)</t>
+          <t>Below 200-DMA (-2.6%)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1791,369 +2242,425 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>29/100</t>
+          <t>59/100</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>above 200-DMA +8.5%; calm vol (0th pctile); near 52w high; RSI 56; sector rank 29/100; regime cautious</t>
+          <t>below 200-DMA -2.6%; calm vol (2th pctile); 36% of 52w range; RSI 66; sector rank 59/100; regime cautious</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>6 months (6M)</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 72; TATACOMM: 55, INDUSTOWER: 40</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>87</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>37768</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>12.7</v>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.5%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+        <v>30426</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8457</v>
+        <v>5241</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8242 - 8672</t>
+          <t>5103 - 5379</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8959</v>
+        <v>4835</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9</v>
+        <v>-7.7</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>-7.7</v>
       </c>
       <c r="J6" t="n">
-        <v>12.2</v>
+        <v>-38.3</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1</v>
+        <v>-0.8</v>
       </c>
       <c r="L6" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>11.2</v>
+        <v>-9.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.2%)</t>
+          <t>Below 200-DMA (-9.6%)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Outperforming</t>
+          <t>Lagging</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>94/100</t>
+          <t>29/100</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>above 200-DMA +11.2%; calm vol (1th pctile); near 52w high; RSI 63; sector rank 94/100; regime cautious</t>
+          <t>below 200-DMA -9.6%; calm vol (2th pctile); near 52w low; RSI 69; sector rank 29/100; regime cautious</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>6 months (6M)</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 26; TATACONSUM: 81, MARICO: 78, NESTLEIND: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>55</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA6" t="n">
-        <v>33828</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>12.3</v>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>26205</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AE6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+11.2%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+      <c r="AI6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.6%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1338.3</v>
+        <v>821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1300 - 1377</t>
+          <t>801 - 841</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1409</v>
+        <v>848</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.7</v>
+        <v>21.8</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
       </c>
       <c r="L7" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>18.3</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.4</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q7" t="n">
+        <v>56</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>86</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Above 200-DMA (+8.5%)</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>In-line</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>29/100</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>above 200-DMA +8.5%; calm vol (0th pctile); near 52w high; RSI 56; sector rank 29/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 78; TATACONSUM: 81, NESTLEIND: 76, VBL: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
         <v>78</v>
       </c>
-      <c r="R7" t="n">
-        <v>6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>47</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-0.6%)</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>In-line</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>35/100</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>below 200-DMA -0.6%; calm vol (6th pctile); 47% of 52w range; RSI 78 (overbought); sector rank 35/100; regime cautious</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6 months (6M)</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA7" t="n">
-        <v>33458</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11.2</v>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.6%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+        <v>27095</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>33</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.5%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5241</v>
+        <v>1309.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5103 - 5379</t>
+          <t>1268 - 1351</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4835</v>
+        <v>1366</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.7</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>-7.7</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>-14.9</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L8" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>18.7</v>
       </c>
       <c r="O8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-4.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-9.6</v>
+        <v>-7.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.6%)</t>
+          <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2163,49 +2670,67 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>29/100</t>
+          <t>18/100</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>below 200-DMA -9.6%; calm vol (2th pctile); near 52w low; RSI 69; sector rank 29/100; regime cautious</t>
+          <t>below 200-DMA -7.8%; calm vol (10th pctile); near 52w low; RSI 49; sector rank 18/100; regime cautious</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>6 months (6M)</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 53; PETRONET: 64, GAIL: 60, ONGC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>72</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA8" t="n">
-        <v>31446</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11</v>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.6%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+        <v>22262</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2771,7 @@
         <v>7.7</v>
       </c>
       <c r="J9" t="n">
-        <v>16.1</v>
+        <v>56.3</v>
       </c>
       <c r="K9" t="n">
         <v>0.9</v>
@@ -2297,39 +2822,627 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6 months (6M)</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 56; LICI: 96, SBIN: 84, BAJAJHLDNG: 81. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>68</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA9" t="n">
-        <v>31173</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10.4</v>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>20171</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AE9" t="n">
+      <c r="AI9" t="n">
         <v>2</v>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>Low-risk Financials holding (low vol) • below 200-dma (-2.5%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>64</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1338.3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1300 - 1377</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1409</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>75</v>
+      </c>
+      <c r="M10" t="n">
+        <v>25</v>
+      </c>
+      <c r="N10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>78</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>47</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-0.6%)</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>In-line</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>35/100</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>below 200-DMA -0.6%; calm vol (6th pctile); 47% of 52w range; RSI 78 (overbought); sector rank 35/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 64; LICI: 96, SBIN: 84, BAJAJHLDNG: 81. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>17398</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.6%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>86</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>354 - 375</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>406</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No historical analogues yet (&lt;3 obs)</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>48</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Above 200-DMA (+2.7%)</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lagging</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>88/100</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>above 200-DMA +2.7%; calm vol (7th pctile); 50% of 52w range; RSI 48; sector rank 88/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 86; SJVN: 74, POWERGRID: 71, NHPC: 70</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>17136</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>47</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • above 200-dma (+2.7%) • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>71</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>291.9</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>283 - 301</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>328</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" t="n">
+        <v>50</v>
+      </c>
+      <c r="N12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>62</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>58</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Above 200-DMA (+2.1%)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lagging</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>88/100</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>above 200-DMA +2.1%; calm vol (8th pctile); 58% of 52w range; RSI 62; sector rank 88/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 71; NTPC: 86, SJVN: 74, NHPC: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>16349</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>56</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • above 200-dma (+2.1%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>33</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25035</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>24271 - 25799</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>23115</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-38</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>53</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" t="n">
+        <v>24</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-5.5%)</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>In-line</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>12/100</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>below 200-DMA -5.5%; calm vol (8th pctile); 24% of 52w range; RSI 53; sector rank 12/100; regime cautious</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SHREECEM: 33; GRASIM: 95, ULTRACEMCO: 66, JKCEMENT: 40. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Low-risk Cement holding (low vol) • below 200-dma (-5.5%) • sector strength 12/100 • regime cautious (partial deploy) • 5 similar past recs: 40% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2394,7 +3507,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17 sectors in universe</t>
+          <t>17 sectors · breadth 51% above 200-DMA</t>
         </is>
       </c>
     </row>
@@ -2423,7 +3536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15 low-vol names</t>
+          <t>12 low-vol names (dynamic N=12)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2621,7 +3734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2679,7 +3792,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -2690,7 +3803,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6 months (6M)</t>
+          <t>2 months (2M)</t>
         </is>
       </c>
     </row>
@@ -2702,7 +3815,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>+2.5%</t>
         </is>
       </c>
     </row>
@@ -2714,7 +3827,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rs537,500</t>
+          <t>Rs512,500</t>
         </is>
       </c>
     </row>
@@ -2726,7 +3839,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rs616,000</t>
+          <t>Rs602,000</t>
         </is>
       </c>
     </row>
@@ -2738,7 +3851,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rs433,500</t>
+          <t>Rs458,000</t>
         </is>
       </c>
     </row>
@@ -2750,7 +3863,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>67%</t>
         </is>
       </c>
     </row>
@@ -2774,7 +3887,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -2786,7 +3899,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -2827,7 +3940,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2842,7 +3955,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2857,7 +3970,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2867,16 +3980,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -2887,7 +4000,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2897,32 +4010,77 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CASH (intentional)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>8 stocks / 5 sectors</t>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>12 stocks / 8 sectors</t>
         </is>
       </c>
     </row>
@@ -28567,674 +29725,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Overall (all history)</t>
+          <t>Horizon</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Win Rate %</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Median Return %</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Beat Nifty %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Worst Cycle %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe (ann)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Chosen</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Years covered</t>
+          <t>1W</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6 (2021-2026)</t>
-        </is>
-      </c>
+          <t>TACTICAL</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>57</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Investment cycles</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>19</v>
-      </c>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TACTICAL</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total stock-picks</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>285</v>
-      </c>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TACTICAL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>57</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Win rate (picks)</t>
+          <t>2M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>OPPORTUNITY</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>67</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>67</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>&lt;-- engine pick (regime)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Median pick return</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+3.3%</t>
-        </is>
-      </c>
+          <t>OPPORTUNITY</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>66</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>73</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Average pick return</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+4.5%</t>
-        </is>
-      </c>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>70</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>64</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cycles beating Nifty</t>
+          <t>9M</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13/19 (68%)</t>
-        </is>
-      </c>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>68</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>64</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Money diary (ref capital)</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>Picks</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Avg Return %</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>Median %</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>Best %</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>Worst %</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>Cycles</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>Beat Nifty</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>Profit Rs</t>
-        </is>
-      </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>Year Ret %</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>End Rs (from ref)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C12" t="n">
-        <v>19</v>
-      </c>
-      <c r="D12" t="n">
-        <v>11</v>
-      </c>
-      <c r="E12" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>43738</v>
-      </c>
-      <c r="M12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>542732</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B13" t="n">
-        <v>60</v>
-      </c>
-      <c r="C13" t="n">
-        <v>32</v>
-      </c>
-      <c r="D13" t="n">
-        <v>28</v>
-      </c>
-      <c r="E13" t="n">
-        <v>53</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>101.2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-19.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>93560</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>600703</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B14" t="n">
-        <v>60</v>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="n">
-        <v>83</v>
-      </c>
-      <c r="F14" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>176947</v>
-      </c>
-      <c r="M14" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>722531</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B15" t="n">
-        <v>60</v>
-      </c>
-      <c r="C15" t="n">
-        <v>37</v>
-      </c>
-      <c r="D15" t="n">
-        <v>23</v>
-      </c>
-      <c r="E15" t="n">
-        <v>62</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-26</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>56158</v>
-      </c>
-      <c r="M15" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>551527</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B16" t="n">
-        <v>60</v>
-      </c>
-      <c r="C16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E16" t="n">
-        <v>58</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-23.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>15954</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>531876</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B17" t="n">
-        <v>15</v>
-      </c>
-      <c r="C17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>7126</v>
-      </c>
-      <c r="M17" t="n">
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>77</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.8</v>
       </c>
-      <c r="N17" t="n">
-        <v>504000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Total cycles</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cycles beating Nifty</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>13 (68%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Cycles positive</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>14 (74%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Avg portfolio return</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>+4.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Median portfolio return</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>+3.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Std deviation</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Avg outperformance vs Nifty</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>+2.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Best cycle</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>+14.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Worst cycle</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>-6.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Avg winning cycle</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>+7.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Avg losing cycle</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>-2.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Median winning cycle</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>+5.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Median losing cycle</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>-1.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Avg holding period</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>6 months (63 trading days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Avg drawdown during hold</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>-5.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Longest win streak</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>9 cycles</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Longest loss streak</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>3 cycles</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29247,162 +30054,672 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Overall (all history)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>How it works</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Selection</t>
+          <t>Years covered</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pick the lowest trailing-volatility names (the only signal with out-of-sample skill).</t>
+          <t>6 (2021-2026)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sector cap</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>At most 2 stocks per sector — forced diversification, not a bet.</t>
-        </is>
+          <t>Investment cycles</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weighting</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hierarchical Risk Parity (HRP): correlation-cluster aware, down-weights crowded risk.</t>
-        </is>
+          <t>Total stock-picks</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>285</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regime overlay</t>
+          <t>Win rate (picks)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scale exposure by market state (India VIX + Nifty 200-DMA + global risk). The single biggest validated edge — de-risks in weak regimes.</t>
+          <t>64%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rebalance</t>
+          <t>Median pick return</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quarterly (beats monthly net of cost; less churn).</t>
+          <t>+3.3%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Evidence gate</t>
+          <t>Average pick return</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Promote nothing on intuition: DSR / PBO / rolling OOS / forward paper.</t>
+          <t>+4.5%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Evidence Score (0-100)</t>
+          <t>Cycles beating Nifty</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Strength label is driven by a transparent score: historical win rate (30) + historical median return (30) + trend/relative-strength (20) + regime &amp; low-vol (20). &gt;=70 STRONG BUY, &gt;=55 BUY, &gt;=42 ACCUMULATE, else WATCH. HARD RULE: a negative historical median is always WATCH (never a BUY), even if held for diversification.</t>
+          <t>13/19 (68%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sector Score (x/100)</t>
+          <t>Money diary (ref capital)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Percentile rank of the stock's sector by 3-month sector momentum. CONTEXT only — it failed the incremental-value test, so it informs but does not drive selection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Today's Setup</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Descriptive current-state facts (distance from 200-DMA, volatility percentile, 52-week range position, RSI, sector rank, regime). Context for 'why today', NOT a forecast.</t>
+          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Holding period</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Chosen from the backtested Horizon Matrix each run (currently 6M). Evidence-selected, not hand-set; it moves if the evidence moves. Per-STOCK horizons are NOT offered — small-sample horizon skill is ~random (RQS 0.5).</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Picks</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Return %</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Median %</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Best %</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Worst %</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Cycles</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Beat Nifty</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Profit Rs</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Year Ret %</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>End Rs (from ref)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Number of holdings</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Driven by how many names clear the low-vol + sector-cap filter (varies by breadth), NOT return-optimised. Tested: choosing N by trailing performance LOSES out-of-sample (Sharpe 0.95 vs 1.24) — so N is risk-driven, and the validated de-risking lever is exposure/cash.</t>
-        </is>
+      <c r="A12" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>43738</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>542732</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>What it does NOT do</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Predict returns or pick 'winners'. Returns are ~unpredictable on this data; risk is. AEGIS forecasts risk, not direction.</t>
+      <c r="A13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B13" t="n">
+        <v>60</v>
+      </c>
+      <c r="C13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D13" t="n">
+        <v>28</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>93560</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>600703</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B14" t="n">
+        <v>60</v>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>83</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>176947</v>
+      </c>
+      <c r="M14" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>722531</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B15" t="n">
+        <v>60</v>
+      </c>
+      <c r="C15" t="n">
+        <v>37</v>
+      </c>
+      <c r="D15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E15" t="n">
+        <v>62</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-26</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>56158</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>551527</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B16" t="n">
+        <v>60</v>
+      </c>
+      <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>58</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>15954</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>531876</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>7126</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>504000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total cycles</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cycles beating Nifty</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13 (68%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cycles positive</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14 (74%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Avg portfolio return</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Median portfolio return</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>+3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Std deviation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Avg outperformance vs Nifty</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>+2.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Best cycle</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>+14.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Worst cycle</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-6.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Avg winning cycle</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Avg losing cycle</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Median winning cycle</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>+5.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Median losing cycle</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>-1.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Avg holding period</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2 months (63 trading days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Avg drawdown during hold</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Longest win streak</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>9 cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Longest loss streak</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3 cycles</t>
         </is>
       </c>
     </row>
@@ -29417,198 +30734,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Detail</t>
+          <t>How it works</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>What AEGIS is</t>
+          <t>Selection</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A risk-managed PORTFOLIO engine: low-volatility selection + HRP weighting + sector cap + market-regime exposure timing. Rebalances quarterly.</t>
+          <t>Pick the lowest trailing-volatility names (the only signal with out-of-sample skill).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>What is validated</t>
+          <t>Sector cap</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The PORTFOLIO process (grade A): beat Nifty 68% of cycles, ~half the drawdown, higher risk-adjusted return. Out-of-sample tested.</t>
+          <t>At most 2 stocks per sector — forced diversification, not a bet.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>What is NOT validated</t>
+          <t>Weighting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Individual stock-picking ALPHA. Selection RQS 0.51 ~ random — picks are portfolio CONSTITUENTS, not proven winners.</t>
+          <t>Hierarchical Risk Parity (HRP): correlation-cluster aware, down-weights crowded risk.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>What AEGIS is NOT</t>
+          <t>Regime overlay</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Not a tip sheet, not a multibagger finder, not a return predictor. It does not forecast which stock will rise.</t>
+          <t>Scale exposure by market state (India VIX + Nifty 200-DMA + global risk). The single biggest validated edge — de-risks in weak regimes.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Exit philosophy</t>
+          <t>Rebalance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Process-based: hold to the quarterly review/rebalance. No fixed stop-loss (unvalidated). Emergency exit only on fraud/delisting/regime-off.</t>
+          <t>Quarterly (beats monthly net of cost; less churn).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Review frequency</t>
+          <t>Evidence gate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quarterly. Recommendation valid ~1 week from generation.</t>
+          <t>Promote nothing on intuition: DSR / PBO / rolling OOS / forward paper.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Not evaluated (no data)</t>
+          <t>Evidence Score (0-100)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fundamentals (ROE/PE/EPS), news/events, earnings, institutional flow. Shown as 'Not Evaluated' — never invented.</t>
+          <t>The Strength label is driven by a transparent score: historical win rate (30) + historical median return (30) + trend/relative-strength (20) + regime &amp; low-vol (20). &gt;=70 STRONG BUY, &gt;=55 BUY, &gt;=42 ACCUMULATE, else WATCH. HARD RULE: a negative historical median is always WATCH (never a BUY), even if held for diversification.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Honest caveat</t>
+          <t>Sector Score (x/100)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Absolute return levels are survivorship-inflated; trust the RELATIVE edge vs Nifty. Forward paper (live cycles) is the real, ongoing test.</t>
+          <t>Percentile rank of the stock's sector by 3-month sector momentum. CONTEXT only — it failed the incremental-value test, so it informs but does not drive selection.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Today's Setup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Descriptive current-state facts (distance from 200-DMA, volatility percentile, 52-week range position, RSI, sector rank, regime). Context for 'why today', NOT a forecast.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EVIDENCE STATUS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Holding period (DYNAMIC)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chosen by choose_horizon() from the backtested Horizon Matrix, REGIME-CONDITIONAL: risk-off favours a strong SHORT horizon (de-risk fast), risk-on lets it run longer. Today: 2M. The full menu of horizons (1W-1Y) with win rates is on this sheet so you can pick a shorter commitment. Per-STOCK horizons are NOT offered (small-sample skill ~random).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Portfolio Strategy</t>
+          <t>Number of holdings (DYNAMIC)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VALIDATED — grade A · beat Nifty 68% of cycles</t>
+          <t>Sized by choose_topn() from market BREADTH (% above 200-DMA) + regime: wider book when healthy, concentrate + more cash when weak. Risk-first, NOT return-tuned (return-tuning N loses OOS). Walk-forward tested: dynamic ~ fixed Sharpe with LOWER drawdown.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stock Selection (alpha)</t>
+          <t>What it does NOT do</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EXPERIMENTAL — RQS 0.51 ~ random · holdings, not bets</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Recommendation Horizon</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>HISTORICALLY TESTED — all horizons backtested · best = 6M</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Technical Context</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>COMPUTED (not a driver) — momentum / rel-strength / 200-DMA shown for info</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fundamental Analysis</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NOT EVALUATED — no point-in-time data</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>News / Events</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NOT EVALUATED — no event database</t>
+          <t>Predict returns or pick 'winners'. Returns are ~unpredictable on this data; risk is. AEGIS forecasts risk, not direction.</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_2026-06-25.xlsx
+++ b/reports/AEGIS_2026-06-25.xlsx
@@ -893,11 +893,15 @@
       <c r="F36" t="n">
         <v>11.3</v>
       </c>
-      <c r="G36" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>100</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -908,7 +912,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -932,12 +936,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -971,11 +975,15 @@
       <c r="F38" t="n">
         <v>10.9</v>
       </c>
-      <c r="G38" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H38" t="n">
-        <v>75</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1045,11 +1053,15 @@
       <c r="F40" t="n">
         <v>10</v>
       </c>
-      <c r="G40" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="H40" t="n">
-        <v>33</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1082,11 +1094,15 @@
       <c r="F41" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>100</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1097,7 +1113,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1156,11 +1172,15 @@
       <c r="F43" t="n">
         <v>7.1</v>
       </c>
-      <c r="G43" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H43" t="n">
-        <v>50</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -1230,11 +1250,15 @@
       <c r="F45" t="n">
         <v>5.8</v>
       </c>
-      <c r="G45" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H45" t="n">
-        <v>100</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -1267,11 +1291,15 @@
       <c r="F46" t="n">
         <v>5.5</v>
       </c>
-      <c r="G46" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>50</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -1533,7 +1561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:AO13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1574,145 +1602,170 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Expected Return Range</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Upside %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Hist Median Ret %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Annualized %</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Risk / Reward (hist)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Probability Positive %</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Probability &gt;10% %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Best Case %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Worst Case %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>F: Historical</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>F: Technical/Trend</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>F: Risk/Vol</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>F: Sector</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>F: Regime</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Dist 200-DMA %</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Vol Pctile</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>52W Range Pos %</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Rel Strength</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Sector Score</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Today's Setup</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Why This vs Alternatives</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Rec Confidence %</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Recommended Holding</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Expected Exit</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Generated</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Valid Until</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Allocation Rs</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Similar Past Cases</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
@@ -1725,7 +1778,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1745,118 +1798,149 @@
           <t>24850 - 26290</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>31853</v>
-      </c>
-      <c r="H2" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>273.7</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" t="n">
-        <v>100</v>
-      </c>
-      <c r="N2" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="P2" t="n">
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>70</v>
+      </c>
+      <c r="R2" t="n">
+        <v>21</v>
+      </c>
+      <c r="S2" t="n">
+        <v>96</v>
+      </c>
+      <c r="T2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U2" t="n">
+        <v>60</v>
+      </c>
+      <c r="V2" t="n">
         <v>-8.6</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="W2" t="n">
         <v>40</v>
       </c>
-      <c r="R2" t="n">
+      <c r="X2" t="n">
         <v>4</v>
       </c>
-      <c r="S2" t="n">
+      <c r="Y2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Below 200-DMA (-8.6%)</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Lagging</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>65/100</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>below 200-DMA -8.6%; calm vol (4th pctile); near 52w low; RSI 40; sector rank 65/100; regime cautious</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 76; CIPLA: 91, TORNTPHARM: 83, SUNPHARMA: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 65; TORNTPHARM: 78, CIPLA: 73, ZYDUSLIFE: 72. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>72</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE2" t="n">
+      <c r="AJ2" t="n">
         <v>25570</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AK2" t="n">
         <v>1</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AL2" t="n">
         <v>11.3</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AI2" t="n">
+      <c r="AN2" t="n">
         <v>2</v>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>Low-risk Pharma holding (low vol) • below 200-dma (-8.6%) • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
         </is>
@@ -1865,11 +1949,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1891,132 +1975,147 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
+          <t>No analogues yet</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
+          <t>No analogues yet</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>No analogues yet</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" t="n">
+        <v>77</v>
+      </c>
+      <c r="S3" t="n">
+        <v>99</v>
+      </c>
+      <c r="T3" t="n">
+        <v>65</v>
+      </c>
+      <c r="U3" t="n">
+        <v>60</v>
+      </c>
+      <c r="V3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="W3" t="n">
         <v>69</v>
       </c>
-      <c r="R3" t="n">
+      <c r="X3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
+      <c r="Y3" t="n">
         <v>83</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Above 200-DMA (+9.3%)</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>In-line</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>65/100</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>above 200-DMA +9.3%; calm vol (1th pctile); near 52w high; RSI 69; sector rank 65/100; regime cautious</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 55; CIPLA: 91, TORNTPHARM: 83, ABBOTINDIA: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 71; TORNTPHARM: 78, CIPLA: 73, ZYDUSLIFE: 72. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>72</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE3" t="n">
+      <c r="AJ3" t="n">
         <v>33009</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AK3" t="n">
         <v>14</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AL3" t="n">
         <v>11</v>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="AI3" t="n">
+      <c r="AN3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.3%) • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
@@ -2049,116 +2148,149 @@
           <t>8242 - 8672</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>8959</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>75</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>64</v>
+      </c>
+      <c r="R4" t="n">
+        <v>88</v>
+      </c>
+      <c r="S4" t="n">
+        <v>99</v>
+      </c>
+      <c r="T4" t="n">
+        <v>94</v>
+      </c>
+      <c r="U4" t="n">
+        <v>60</v>
+      </c>
+      <c r="V4" t="n">
         <v>11.2</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="W4" t="n">
         <v>63</v>
       </c>
-      <c r="R4" t="n">
+      <c r="X4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
+      <c r="Y4" t="n">
         <v>96</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Above 200-DMA (+11.2%)</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Outperforming</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>94/100</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>above 200-DMA +11.2%; calm vol (1th pctile); near 52w high; RSI 63; sector rank 94/100; regime cautious</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 80; FORTIS: 60, MAXHEALTH: 60, LALPATHLAB: 55</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 80; FORTIS: 72, MAXHEALTH: 70, METROPOLIS: 64</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
         <v>79</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE4" t="n">
+      <c r="AJ4" t="n">
         <v>25371</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AK4" t="n">
         <v>3</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AL4" t="n">
         <v>10.9</v>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AI4" t="n">
+      <c r="AN4" t="n">
         <v>4</v>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>Low-risk Healthcare holding (low vol) • above 200-dma (+11.2%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
@@ -2171,7 +2303,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2194,113 +2326,128 @@
       <c r="G5" t="n">
         <v>2139</v>
       </c>
-      <c r="H5" t="n">
-        <v>12.5</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-2.8% to +14.8% (mid 50% of 13 cases)</t>
+        </is>
       </c>
       <c r="I5" t="n">
         <v>12.5</v>
       </c>
       <c r="J5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K5" t="n">
         <v>102.3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1.3</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>69</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>54</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>29.3</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>-9.5</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>76</v>
+      </c>
+      <c r="R5" t="n">
+        <v>37</v>
+      </c>
+      <c r="S5" t="n">
+        <v>98</v>
+      </c>
+      <c r="T5" t="n">
+        <v>59</v>
+      </c>
+      <c r="U5" t="n">
+        <v>60</v>
+      </c>
+      <c r="V5" t="n">
         <v>-2.6</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="W5" t="n">
         <v>66</v>
       </c>
-      <c r="R5" t="n">
+      <c r="X5" t="n">
         <v>2</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Y5" t="n">
         <v>36</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Below 200-DMA (-2.6%)</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>In-line</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>59/100</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>below 200-DMA -2.6%; calm vol (2th pctile); 36% of 52w range; RSI 66; sector rank 59/100; regime cautious</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 72; TATACOMM: 55, INDUSTOWER: 40</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 70; TATACOMM: 54, INDUSTOWER: 52</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>86</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE5" t="n">
+      <c r="AJ5" t="n">
         <v>30426</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AK5" t="n">
         <v>16</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AL5" t="n">
         <v>10.2</v>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AI5" t="n">
+      <c r="AN5" t="n">
         <v>13</v>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
@@ -2313,7 +2460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2333,116 +2480,149 @@
           <t>5103 - 5379</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>4835</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-38.3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>33</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>32</v>
+      </c>
+      <c r="R6" t="n">
+        <v>23</v>
+      </c>
+      <c r="S6" t="n">
+        <v>98</v>
+      </c>
+      <c r="T6" t="n">
+        <v>29</v>
+      </c>
+      <c r="U6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V6" t="n">
         <v>-9.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="W6" t="n">
         <v>69</v>
       </c>
-      <c r="R6" t="n">
+      <c r="X6" t="n">
         <v>2</v>
       </c>
-      <c r="S6" t="n">
+      <c r="Y6" t="n">
         <v>14</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Below 200-DMA (-9.6%)</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Lagging</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>29/100</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>below 200-DMA -9.6%; calm vol (2th pctile); near 52w low; RSI 69; sector rank 29/100; regime cautious</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 26; TATACONSUM: 81, MARICO: 78, NESTLEIND: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; NESTLEIND: 74, MARICO: 72, VBL: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>66</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE6" t="n">
+      <c r="AJ6" t="n">
         <v>26205</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AK6" t="n">
         <v>5</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AL6" t="n">
         <v>10</v>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AI6" t="n">
+      <c r="AN6" t="n">
         <v>3</v>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.6%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
@@ -2455,7 +2635,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2475,118 +2655,149 @@
           <t>801 - 841</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>848</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21.8</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>61</v>
+      </c>
+      <c r="R7" t="n">
+        <v>84</v>
+      </c>
+      <c r="S7" t="n">
         <v>100</v>
       </c>
-      <c r="M7" t="n">
+      <c r="T7" t="n">
+        <v>29</v>
+      </c>
+      <c r="U7" t="n">
+        <v>60</v>
+      </c>
+      <c r="V7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>56</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>56</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="Y7" t="n">
         <v>86</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Above 200-DMA (+8.5%)</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>In-line</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>29/100</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>above 200-DMA +8.5%; calm vol (0th pctile); near 52w high; RSI 56; sector rank 29/100; regime cautious</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 78; TATACONSUM: 81, NESTLEIND: 76, VBL: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 72; NESTLEIND: 74, VBL: 58, TATACONSUM: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE7" t="n">
+      <c r="AJ7" t="n">
         <v>27095</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AK7" t="n">
         <v>33</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AL7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AI7" t="n">
+      <c r="AN7" t="n">
         <v>2</v>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.5%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
@@ -2595,11 +2806,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2622,113 +2833,128 @@
       <c r="G8" t="n">
         <v>1366</v>
       </c>
-      <c r="H8" t="n">
-        <v>4.3</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.4% to +7.0% (mid 50% of 8 cases)</t>
+        </is>
       </c>
       <c r="I8" t="n">
         <v>4.3</v>
       </c>
       <c r="J8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K8" t="n">
         <v>29</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.9</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>62</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>12</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>18.7</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-4.9</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
+        <v>56</v>
+      </c>
+      <c r="R8" t="n">
+        <v>26</v>
+      </c>
+      <c r="S8" t="n">
+        <v>90</v>
+      </c>
+      <c r="T8" t="n">
+        <v>18</v>
+      </c>
+      <c r="U8" t="n">
+        <v>60</v>
+      </c>
+      <c r="V8" t="n">
         <v>-7.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="W8" t="n">
         <v>49</v>
       </c>
-      <c r="R8" t="n">
+      <c r="X8" t="n">
         <v>10</v>
       </c>
-      <c r="S8" t="n">
+      <c r="Y8" t="n">
         <v>15</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Lagging</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>18/100</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>below 200-DMA -7.8%; calm vol (10th pctile); near 52w low; RSI 49; sector rank 18/100; regime cautious</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 53; PETRONET: 64, GAIL: 60, ONGC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>72</v>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 55; GAIL: 60, IGL: 52, PETRONET: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE8" t="n">
+      <c r="AJ8" t="n">
         <v>22262</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AK8" t="n">
         <v>17</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AL8" t="n">
         <v>7.7</v>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AI8" t="n">
+      <c r="AN8" t="n">
         <v>8</v>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
@@ -2741,7 +2967,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2761,116 +2987,149 @@
           <t>1782 - 1885</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>1975</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>50</v>
-      </c>
-      <c r="M9" t="n">
-        <v>50</v>
-      </c>
-      <c r="N9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>52</v>
+      </c>
+      <c r="R9" t="n">
+        <v>34</v>
+      </c>
+      <c r="S9" t="n">
+        <v>97</v>
+      </c>
+      <c r="T9" t="n">
+        <v>35</v>
+      </c>
+      <c r="U9" t="n">
+        <v>60</v>
+      </c>
+      <c r="V9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="W9" t="n">
         <v>62</v>
       </c>
-      <c r="R9" t="n">
+      <c r="X9" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="Y9" t="n">
         <v>39</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Below 200-DMA (-2.5%)</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Lagging</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>35/100</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>below 200-DMA -2.5%; calm vol (3th pctile); 39% of 52w range; RSI 62; sector rank 35/100; regime cautious</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 56; LICI: 96, SBIN: 84, BAJAJHLDNG: 81. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
-        <v>68</v>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 59; AXISBANK: 62, ICICIBANK: 62, KOTAKBANK: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE9" t="n">
+      <c r="AJ9" t="n">
         <v>20171</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AK9" t="n">
         <v>11</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AL9" t="n">
         <v>7.1</v>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AI9" t="n">
+      <c r="AN9" t="n">
         <v>2</v>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Low-risk Financials holding (low vol) • below 200-dma (-2.5%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
         </is>
@@ -2883,7 +3142,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2906,113 +3165,128 @@
       <c r="G10" t="n">
         <v>1409</v>
       </c>
-      <c r="H10" t="n">
-        <v>5.3</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>+1.6% to +8.1% (mid 50% of 8 cases)</t>
+        </is>
       </c>
       <c r="I10" t="n">
         <v>5.3</v>
       </c>
       <c r="J10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K10" t="n">
         <v>36.5</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>75</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>25</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>18.3</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-7.4</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
+        <v>66</v>
+      </c>
+      <c r="R10" t="n">
+        <v>29</v>
+      </c>
+      <c r="S10" t="n">
+        <v>94</v>
+      </c>
+      <c r="T10" t="n">
+        <v>35</v>
+      </c>
+      <c r="U10" t="n">
+        <v>60</v>
+      </c>
+      <c r="V10" t="n">
         <v>-0.6</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="W10" t="n">
         <v>78</v>
       </c>
-      <c r="R10" t="n">
+      <c r="X10" t="n">
         <v>6</v>
       </c>
-      <c r="S10" t="n">
+      <c r="Y10" t="n">
         <v>47</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Below 200-DMA (-0.6%)</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>In-line</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>35/100</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>below 200-DMA -0.6%; calm vol (6th pctile); 47% of 52w range; RSI 78 (overbought); sector rank 35/100; regime cautious</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 64; LICI: 96, SBIN: 84, BAJAJHLDNG: 81. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="Y10" t="n">
-        <v>77</v>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 62; AXISBANK: 62, KOTAKBANK: 62, LICI: 62</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>76</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE10" t="n">
+      <c r="AJ10" t="n">
         <v>17398</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AK10" t="n">
         <v>13</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AL10" t="n">
         <v>5.9</v>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AI10" t="n">
+      <c r="AN10" t="n">
         <v>8</v>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>Low-risk Financials holding (low vol) • below 200-dma (-0.6%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
@@ -3025,7 +3299,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3045,118 +3319,149 @@
           <t>354 - 375</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>406</v>
-      </c>
-      <c r="H11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>91.7</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>No historical analogues yet (&lt;3 obs)</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>100</v>
-      </c>
-      <c r="M11" t="n">
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>84</v>
+      </c>
+      <c r="R11" t="n">
+        <v>70</v>
+      </c>
+      <c r="S11" t="n">
+        <v>93</v>
+      </c>
+      <c r="T11" t="n">
+        <v>88</v>
+      </c>
+      <c r="U11" t="n">
+        <v>60</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>48</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y11" t="n">
         <v>50</v>
       </c>
-      <c r="N11" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>48</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Above 200-DMA (+2.7%)</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Lagging</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>88/100</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>above 200-DMA +2.7%; calm vol (7th pctile); 50% of 52w range; RSI 48; sector rank 88/100; regime cautious</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 86; SJVN: 74, POWERGRID: 71, NHPC: 70</t>
-        </is>
-      </c>
-      <c r="Y11" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 80; POWERGRID: 72, TATAPOWER: 68, CESC: 62</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>79</v>
+      </c>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE11" t="n">
+      <c r="AJ11" t="n">
         <v>17136</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AK11" t="n">
         <v>47</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AL11" t="n">
         <v>5.8</v>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AI11" t="n">
+      <c r="AN11" t="n">
         <v>4</v>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>Low-risk Power holding (low vol) • above 200-dma (+2.7%) • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
@@ -3169,7 +3474,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3189,116 +3494,149 @@
           <t>283 - 301</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>328</v>
-      </c>
-      <c r="H12" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>50</v>
-      </c>
-      <c r="M12" t="n">
-        <v>50</v>
-      </c>
-      <c r="N12" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Insufficient evidence (&lt;5 cases)</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>56</v>
+      </c>
+      <c r="R12" t="n">
+        <v>71</v>
+      </c>
+      <c r="S12" t="n">
+        <v>92</v>
+      </c>
+      <c r="T12" t="n">
+        <v>88</v>
+      </c>
+      <c r="U12" t="n">
+        <v>60</v>
+      </c>
+      <c r="V12" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="W12" t="n">
         <v>62</v>
       </c>
-      <c r="R12" t="n">
+      <c r="X12" t="n">
         <v>8</v>
       </c>
-      <c r="S12" t="n">
+      <c r="Y12" t="n">
         <v>58</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Above 200-DMA (+2.1%)</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Lagging</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>88/100</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>above 200-DMA +2.1%; calm vol (8th pctile); 58% of 52w range; RSI 62; sector rank 88/100; regime cautious</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 71; NTPC: 86, SJVN: 74, NHPC: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 72; NTPC: 80, TATAPOWER: 68, CESC: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
         <v>75</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE12" t="n">
+      <c r="AJ12" t="n">
         <v>16349</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AK12" t="n">
         <v>56</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AL12" t="n">
         <v>5.5</v>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AI12" t="n">
+      <c r="AN12" t="n">
         <v>2</v>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>Low-risk Power holding (low vol) • above 200-dma (+2.1%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
@@ -3311,7 +3649,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3334,113 +3672,128 @@
       <c r="G13" t="n">
         <v>23115</v>
       </c>
-      <c r="H13" t="n">
-        <v>-7.7</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-10.6% to +3.4% (mid 50% of 5 cases)</t>
+        </is>
       </c>
       <c r="I13" t="n">
         <v>-7.7</v>
       </c>
       <c r="J13" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="K13" t="n">
         <v>-38</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-0.7</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>40</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>4.6</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>-11.1</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>24</v>
+      </c>
+      <c r="R13" t="n">
+        <v>40</v>
+      </c>
+      <c r="S13" t="n">
+        <v>92</v>
+      </c>
+      <c r="T13" t="n">
+        <v>12</v>
+      </c>
+      <c r="U13" t="n">
+        <v>60</v>
+      </c>
+      <c r="V13" t="n">
         <v>-5.5</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="W13" t="n">
         <v>53</v>
       </c>
-      <c r="R13" t="n">
+      <c r="X13" t="n">
         <v>8</v>
       </c>
-      <c r="S13" t="n">
+      <c r="Y13" t="n">
         <v>24</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Below 200-DMA (-5.5%)</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>In-line</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>12/100</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>below 200-DMA -5.5%; calm vol (8th pctile); 24% of 52w range; RSI 53; sector rank 12/100; regime cautious</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SHREECEM: 33; GRASIM: 95, ULTRACEMCO: 66, JKCEMENT: 40. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="Y13" t="n">
-        <v>63</v>
-      </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SHREECEM: 48; GRASIM: 74, ULTRACEMCO: 56, ACC: 46. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE13" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="AE13" t="n">
+      <c r="AJ13" t="n">
         <v>0</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AK13" t="n">
         <v>0</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AL13" t="n">
         <v>5.4</v>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AI13" t="n">
+      <c r="AN13" t="n">
         <v>5</v>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
         <is>
           <t>Low-risk Cement holding (low vol) • below 200-dma (-5.5%) • sector strength 12/100 • regime cautious (partial deploy) • 5 similar past recs: 40% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
@@ -30054,7 +30407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30169,67 +30522,72 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
+          <t>Start Rs</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>End Rs</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Year Ret %</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Beat Nifty</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Cycles</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
           <t>Picks</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>Winners</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Losers</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>Avg Return %</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>Median %</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>Best %</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>Worst %</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>Cycles</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>Beat Nifty</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>Profit Rs</t>
-        </is>
-      </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>Year Ret %</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>End Rs (from ref)</t>
         </is>
       </c>
     </row>
@@ -30238,45 +30596,48 @@
         <v>2021</v>
       </c>
       <c r="B12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>542732</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
         <v>30</v>
       </c>
-      <c r="C12" t="n">
+      <c r="H12" t="n">
+        <v>63</v>
+      </c>
+      <c r="I12" t="n">
         <v>19</v>
       </c>
-      <c r="D12" t="n">
+      <c r="J12" t="n">
         <v>11</v>
       </c>
-      <c r="E12" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="K12" t="n">
         <v>4.6</v>
       </c>
-      <c r="G12" t="n">
+      <c r="L12" t="n">
         <v>6</v>
       </c>
-      <c r="H12" t="n">
+      <c r="M12" t="n">
         <v>31.6</v>
       </c>
-      <c r="I12" t="n">
+      <c r="N12" t="n">
         <v>-14.9</v>
       </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
+      <c r="O12" t="n">
         <v>43738</v>
-      </c>
-      <c r="M12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>542732</v>
       </c>
     </row>
     <row r="13">
@@ -30284,45 +30645,48 @@
         <v>2022</v>
       </c>
       <c r="B13" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>600703</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
         <v>60</v>
       </c>
-      <c r="C13" t="n">
+      <c r="H13" t="n">
+        <v>53</v>
+      </c>
+      <c r="I13" t="n">
         <v>32</v>
       </c>
-      <c r="D13" t="n">
+      <c r="J13" t="n">
         <v>28</v>
       </c>
-      <c r="E13" t="n">
-        <v>53</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="K13" t="n">
         <v>4.3</v>
       </c>
-      <c r="G13" t="n">
+      <c r="L13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H13" t="n">
+      <c r="M13" t="n">
         <v>101.2</v>
       </c>
-      <c r="I13" t="n">
+      <c r="N13" t="n">
         <v>-19.8</v>
       </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
         <v>93560</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>600703</v>
       </c>
     </row>
     <row r="14">
@@ -30330,45 +30694,48 @@
         <v>2023</v>
       </c>
       <c r="B14" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>722531</v>
+      </c>
+      <c r="D14" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
         <v>60</v>
       </c>
-      <c r="C14" t="n">
+      <c r="H14" t="n">
+        <v>83</v>
+      </c>
+      <c r="I14" t="n">
         <v>50</v>
       </c>
-      <c r="D14" t="n">
+      <c r="J14" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
-        <v>83</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="K14" t="n">
         <v>9.1</v>
       </c>
-      <c r="G14" t="n">
+      <c r="L14" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H14" t="n">
+      <c r="M14" t="n">
         <v>34.7</v>
       </c>
-      <c r="I14" t="n">
+      <c r="N14" t="n">
         <v>-16.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
+      <c r="O14" t="n">
         <v>176947</v>
-      </c>
-      <c r="M14" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>722531</v>
       </c>
     </row>
     <row r="15">
@@ -30376,45 +30743,48 @@
         <v>2024</v>
       </c>
       <c r="B15" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>551527</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
         <v>60</v>
       </c>
-      <c r="C15" t="n">
+      <c r="H15" t="n">
+        <v>62</v>
+      </c>
+      <c r="I15" t="n">
         <v>37</v>
       </c>
-      <c r="D15" t="n">
+      <c r="J15" t="n">
         <v>23</v>
       </c>
-      <c r="E15" t="n">
-        <v>62</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="K15" t="n">
         <v>3.1</v>
       </c>
-      <c r="G15" t="n">
+      <c r="L15" t="n">
         <v>2.6</v>
       </c>
-      <c r="H15" t="n">
+      <c r="M15" t="n">
         <v>25.9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="N15" t="n">
         <v>-26</v>
       </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
+      <c r="O15" t="n">
         <v>56158</v>
-      </c>
-      <c r="M15" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>551527</v>
       </c>
     </row>
     <row r="16">
@@ -30422,45 +30792,48 @@
         <v>2025</v>
       </c>
       <c r="B16" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>531876</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
         <v>60</v>
       </c>
-      <c r="C16" t="n">
+      <c r="H16" t="n">
+        <v>58</v>
+      </c>
+      <c r="I16" t="n">
         <v>35</v>
       </c>
-      <c r="D16" t="n">
+      <c r="J16" t="n">
         <v>25</v>
       </c>
-      <c r="E16" t="n">
-        <v>58</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="K16" t="n">
         <v>1.9</v>
       </c>
-      <c r="G16" t="n">
+      <c r="L16" t="n">
         <v>1.5</v>
       </c>
-      <c r="H16" t="n">
+      <c r="M16" t="n">
         <v>28.9</v>
       </c>
-      <c r="I16" t="n">
+      <c r="N16" t="n">
         <v>-23.6</v>
       </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>15954</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>531876</v>
       </c>
     </row>
     <row r="17">
@@ -30468,45 +30841,48 @@
         <v>2026</v>
       </c>
       <c r="B17" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C17" t="n">
+        <v>504000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>15</v>
       </c>
-      <c r="C17" t="n">
+      <c r="H17" t="n">
+        <v>60</v>
+      </c>
+      <c r="I17" t="n">
         <v>9</v>
       </c>
-      <c r="D17" t="n">
+      <c r="J17" t="n">
         <v>6</v>
       </c>
-      <c r="E17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="K17" t="n">
         <v>2.2</v>
       </c>
-      <c r="G17" t="n">
+      <c r="L17" t="n">
         <v>2.5</v>
       </c>
-      <c r="H17" t="n">
+      <c r="M17" t="n">
         <v>25.2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="N17" t="n">
         <v>-16.7</v>
       </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
+      <c r="O17" t="n">
         <v>7126</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>504000</v>
       </c>
     </row>
     <row r="19">
@@ -30734,7 +31110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30824,70 +31200,106 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Evidence Score (0-100)</t>
+          <t>Factor breakdown (each 0-100)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Strength label is driven by a transparent score: historical win rate (30) + historical median return (30) + trend/relative-strength (20) + regime &amp; low-vol (20). &gt;=70 STRONG BUY, &gt;=55 BUY, &gt;=42 ACCUMULATE, else WATCH. HARD RULE: a negative historical median is always WATCH (never a BUY), even if held for diversification.</t>
+          <t>Every pick shows 5 sub-scores so you see WHY, not one opaque number: Historical (win rate + median, SHRUNK toward neutral when &lt;5 cases), Technical/Trend (200-DMA, relative strength, RSI), Risk/Vol (low volatility = high), Sector, Regime. Overall = 0.30 Historical + 0.25 Risk + 0.20 Technical + 0.10 Sector + 0.15 Regime.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sector Score (x/100)</t>
+          <t>Strength tiers</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Percentile rank of the stock's sector by 3-month sector momentum. CONTEXT only — it failed the incremental-value test, so it informs but does not drive selection.</t>
+          <t>&gt;=65 STRONG BUY, &gt;=55 BUY, &gt;=45 ACCUMULATE, else WATCH. HARD RULE: a negative historical median is always WATCH (never a BUY), even if held for diversification.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Today's Setup</t>
+          <t>Evidence threshold</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Descriptive current-state facts (distance from 200-DMA, volatility percentile, 52-week range position, RSI, sector rank, regime). Context for 'why today', NOT a forecast.</t>
+          <t>A target price / return range is shown only with &gt;=5 historical analogues; fewer says 'Insufficient evidence'. We never invent a number from a tiny sample.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Holding period (DYNAMIC)</t>
+          <t>Sector Score (x/100)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chosen by choose_horizon() from the backtested Horizon Matrix, REGIME-CONDITIONAL: risk-off favours a strong SHORT horizon (de-risk fast), risk-on lets it run longer. Today: 2M. The full menu of horizons (1W-1Y) with win rates is on this sheet so you can pick a shorter commitment. Per-STOCK horizons are NOT offered (small-sample skill ~random).</t>
+          <t>Percentile rank of the stock's sector by 3-month sector momentum. CONTEXT only — it failed the incremental-value test, so it informs but does not drive selection.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Number of holdings (DYNAMIC)</t>
+          <t>Sector-risk tilt</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sized by choose_topn() from market BREADTH (% above 200-DMA) + regime: wider book when healthy, concentrate + more cash when weak. Risk-first, NOT return-tuned (return-tuning N loses OOS). Walk-forward tested: dynamic ~ fixed Sharpe with LOWER drawdown.</t>
+          <t>A risk-first sector tilt (overweight low-vol sectors) was BUILT and walk-forward VALIDATED — it underperformed (Sharpe 0.99 vs 1.15) so it is kept OFF. Honest: tested, not adopted.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Today's Setup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Descriptive current-state facts (distance from 200-DMA, volatility percentile, 52-week range position, RSI, sector rank, regime). Context for 'why today', NOT a forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Holding period (DYNAMIC)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chosen by choose_horizon() from the backtested Horizon Matrix, REGIME-CONDITIONAL: risk-off favours a strong SHORT horizon (de-risk fast), risk-on lets it run longer. Today: 2M. The full menu of horizons (1W-1Y) with win rates is on this sheet so you can pick a shorter commitment. Per-STOCK horizons are NOT offered (small-sample skill ~random).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Number of holdings (DYNAMIC)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sized by choose_topn() from market BREADTH (% above 200-DMA) + regime: wider book when healthy, concentrate + more cash when weak. Risk-first, NOT return-tuned (return-tuning N loses OOS). Walk-forward tested: dynamic ~ fixed Sharpe with LOWER drawdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>What it does NOT do</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Predict returns or pick 'winners'. Returns are ~unpredictable on this data; risk is. AEGIS forecasts risk, not direction.</t>
         </is>
